--- a/research/traditional_assets/database/data/germany/germany_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_metals_mining.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08841672207118731</v>
+        <v>0.08818297190497375</v>
       </c>
       <c r="C2">
-        <v>3713.375484713865</v>
+        <v>3692.929747099551</v>
       </c>
       <c r="D2">
-        <v>3353.875484713865</v>
+        <v>3372.372747099551</v>
       </c>
       <c r="E2">
-        <v>-427.4</v>
+        <v>-388.457</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38.943</v>
       </c>
       <c r="G2">
         <v>359.5</v>
@@ -1457,28 +1457,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.9588329</v>
       </c>
       <c r="N2">
-        <v>532.5999999999999</v>
+        <v>530.6411671</v>
       </c>
       <c r="O2">
-        <v>159.78</v>
+        <v>159.19235013</v>
       </c>
       <c r="P2">
-        <v>372.8199999999999</v>
+        <v>371.4488169699999</v>
       </c>
       <c r="Q2">
-        <v>597.6199999999999</v>
+        <v>596.24881697</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08841672207118731</v>
+        <v>0.08871805242926642</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652958</v>
+        <v>0.9911790399368685</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>271.8965972033653</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08818297190497375</v>
+        <v>0.0879492217387602</v>
       </c>
       <c r="C3">
-        <v>3692.929747099551</v>
+        <v>3672.6891728538</v>
       </c>
       <c r="D3">
-        <v>3372.372747099551</v>
+        <v>3391.0751728538</v>
       </c>
       <c r="E3">
-        <v>-388.457</v>
+        <v>-349.514</v>
       </c>
       <c r="F3">
-        <v>38.943</v>
+        <v>77.88600000000001</v>
       </c>
       <c r="G3">
         <v>359.5</v>
@@ -1539,28 +1539,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M3">
-        <v>1.9588329</v>
+        <v>3.9176658</v>
       </c>
       <c r="N3">
-        <v>530.6411671</v>
+        <v>528.6823341999999</v>
       </c>
       <c r="O3">
-        <v>159.19235013</v>
+        <v>158.60470026</v>
       </c>
       <c r="P3">
-        <v>371.4488169699999</v>
+        <v>370.0776339399999</v>
       </c>
       <c r="Q3">
-        <v>596.24881697</v>
+        <v>594.8776339399999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08871805242926642</v>
+        <v>0.08902553238649</v>
       </c>
       <c r="T3">
-        <v>0.9911790399368685</v>
+        <v>0.9982801936833714</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>271.8965972033653</v>
+        <v>135.9482986016826</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0879492217387602</v>
+        <v>0.08771547157254662</v>
       </c>
       <c r="C4">
-        <v>3672.6891728538</v>
+        <v>3652.657194382578</v>
       </c>
       <c r="D4">
-        <v>3391.0751728538</v>
+        <v>3409.986194382579</v>
       </c>
       <c r="E4">
-        <v>-349.514</v>
+        <v>-310.571</v>
       </c>
       <c r="F4">
-        <v>77.88600000000001</v>
+        <v>116.829</v>
       </c>
       <c r="G4">
         <v>359.5</v>
@@ -1621,28 +1621,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M4">
-        <v>3.9176658</v>
+        <v>5.8764987</v>
       </c>
       <c r="N4">
-        <v>528.6823341999999</v>
+        <v>526.7235013</v>
       </c>
       <c r="O4">
-        <v>158.60470026</v>
+        <v>158.01705039</v>
       </c>
       <c r="P4">
-        <v>370.0776339399999</v>
+        <v>368.7064509099999</v>
       </c>
       <c r="Q4">
-        <v>594.8776339399999</v>
+        <v>593.50645091</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08902553238649</v>
+        <v>0.08933935213664601</v>
       </c>
       <c r="T4">
-        <v>0.9982801936833714</v>
+        <v>1.005527762971039</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>135.9482986016826</v>
+        <v>90.63219906778843</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08771547157254662</v>
+        <v>0.08748172140633305</v>
       </c>
       <c r="C5">
-        <v>3652.657194382578</v>
+        <v>3632.837321087269</v>
       </c>
       <c r="D5">
-        <v>3409.986194382579</v>
+        <v>3429.109321087269</v>
       </c>
       <c r="E5">
-        <v>-310.571</v>
+        <v>-271.6279999999999</v>
       </c>
       <c r="F5">
-        <v>116.829</v>
+        <v>155.772</v>
       </c>
       <c r="G5">
         <v>359.5</v>
@@ -1703,28 +1703,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M5">
-        <v>5.8764987</v>
+        <v>7.835331600000001</v>
       </c>
       <c r="N5">
-        <v>526.7235013</v>
+        <v>524.7646683999999</v>
       </c>
       <c r="O5">
-        <v>158.01705039</v>
+        <v>157.42940052</v>
       </c>
       <c r="P5">
-        <v>368.7064509099999</v>
+        <v>367.3352678799999</v>
       </c>
       <c r="Q5">
-        <v>593.50645091</v>
+        <v>592.1352678799999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08933935213664601</v>
+        <v>0.0896597097982636</v>
       </c>
       <c r="T5">
-        <v>1.005527762971039</v>
+        <v>1.012926323285533</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>90.63219906778843</v>
+        <v>67.9741493008413</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08748172140633305</v>
+        <v>0.08724797124011949</v>
       </c>
       <c r="C6">
-        <v>3632.837321087269</v>
+        <v>3613.233141535802</v>
       </c>
       <c r="D6">
-        <v>3429.109321087269</v>
+        <v>3448.448141535802</v>
       </c>
       <c r="E6">
-        <v>-271.6279999999999</v>
+        <v>-232.6849999999999</v>
       </c>
       <c r="F6">
-        <v>155.772</v>
+        <v>194.715</v>
       </c>
       <c r="G6">
         <v>359.5</v>
@@ -1785,28 +1785,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M6">
-        <v>7.835331600000001</v>
+        <v>9.794164500000001</v>
       </c>
       <c r="N6">
-        <v>524.7646683999999</v>
+        <v>522.8058354999999</v>
       </c>
       <c r="O6">
-        <v>157.42940052</v>
+        <v>156.84175065</v>
       </c>
       <c r="P6">
-        <v>367.3352678799999</v>
+        <v>365.9640848499999</v>
       </c>
       <c r="Q6">
-        <v>592.1352678799999</v>
+        <v>590.76408485</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0896597097982636</v>
+        <v>0.08998681183170473</v>
       </c>
       <c r="T6">
-        <v>1.012926323285533</v>
+        <v>1.020480642764543</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>67.9741493008413</v>
+        <v>54.37931944067306</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08724797124011949</v>
+        <v>0.08701422107390593</v>
       </c>
       <c r="C7">
-        <v>3613.233141535802</v>
+        <v>3593.848325707653</v>
       </c>
       <c r="D7">
-        <v>3448.448141535802</v>
+        <v>3468.006325707653</v>
       </c>
       <c r="E7">
-        <v>-232.6849999999999</v>
+        <v>-193.742</v>
       </c>
       <c r="F7">
-        <v>194.715</v>
+        <v>233.658</v>
       </c>
       <c r="G7">
         <v>359.5</v>
@@ -1867,28 +1867,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M7">
-        <v>9.794164500000001</v>
+        <v>11.7529974</v>
       </c>
       <c r="N7">
-        <v>522.8058354999999</v>
+        <v>520.8470025999999</v>
       </c>
       <c r="O7">
-        <v>156.84175065</v>
+        <v>156.25410078</v>
       </c>
       <c r="P7">
-        <v>365.9640848499999</v>
+        <v>364.59290182</v>
       </c>
       <c r="Q7">
-        <v>590.76408485</v>
+        <v>589.3929018199999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08998681183170473</v>
+        <v>0.09032087348287865</v>
       </c>
       <c r="T7">
-        <v>1.020480642764543</v>
+        <v>1.028195692445234</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>54.37931944067306</v>
+        <v>45.31609953389421</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08701422107390593</v>
+        <v>0.08678047090769239</v>
       </c>
       <c r="C8">
-        <v>3593.848325707653</v>
+        <v>3574.686627315673</v>
       </c>
       <c r="D8">
-        <v>3468.006325707653</v>
+        <v>3487.787627315673</v>
       </c>
       <c r="E8">
-        <v>-193.742</v>
+        <v>-154.799</v>
       </c>
       <c r="F8">
-        <v>233.658</v>
+        <v>272.601</v>
       </c>
       <c r="G8">
         <v>359.5</v>
@@ -1949,28 +1949,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M8">
-        <v>11.7529974</v>
+        <v>13.7118303</v>
       </c>
       <c r="N8">
-        <v>520.8470025999999</v>
+        <v>518.8881696999999</v>
       </c>
       <c r="O8">
-        <v>156.25410078</v>
+        <v>155.66645091</v>
       </c>
       <c r="P8">
-        <v>364.59290182</v>
+        <v>363.22171879</v>
       </c>
       <c r="Q8">
-        <v>589.3929018199999</v>
+        <v>588.02171879</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09032087348287865</v>
+        <v>0.09066211925558321</v>
       </c>
       <c r="T8">
-        <v>1.028195692445234</v>
+        <v>1.036076657172822</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>45.31609953389421</v>
+        <v>38.84237102905219</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08678047090769238</v>
+        <v>0.08654672074147882</v>
       </c>
       <c r="C9">
-        <v>3574.686627315674</v>
+        <v>3555.751886207849</v>
       </c>
       <c r="D9">
-        <v>3487.787627315674</v>
+        <v>3507.795886207849</v>
       </c>
       <c r="E9">
-        <v>-154.7989999999999</v>
+        <v>-115.8559999999999</v>
       </c>
       <c r="F9">
-        <v>272.6010000000001</v>
+        <v>311.544</v>
       </c>
       <c r="G9">
         <v>359.5</v>
@@ -2031,28 +2031,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M9">
-        <v>13.7118303</v>
+        <v>15.6706632</v>
       </c>
       <c r="N9">
-        <v>518.8881696999999</v>
+        <v>516.9293367999999</v>
       </c>
       <c r="O9">
-        <v>155.66645091</v>
+        <v>155.0788010399999</v>
       </c>
       <c r="P9">
-        <v>363.22171879</v>
+        <v>361.85053576</v>
       </c>
       <c r="Q9">
-        <v>588.02171879</v>
+        <v>586.6505357599999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09066211925558321</v>
+        <v>0.09101078341465089</v>
       </c>
       <c r="T9">
-        <v>1.036076657172822</v>
+        <v>1.044128947220575</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>38.84237102905218</v>
+        <v>33.98707465042065</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08654672074147882</v>
+        <v>0.08631297057526525</v>
       </c>
       <c r="C10">
-        <v>3555.751886207849</v>
+        <v>3537.04803085218</v>
       </c>
       <c r="D10">
-        <v>3507.795886207849</v>
+        <v>3528.03503085218</v>
       </c>
       <c r="E10">
-        <v>-115.8559999999999</v>
+        <v>-76.91299999999995</v>
       </c>
       <c r="F10">
-        <v>311.544</v>
+        <v>350.487</v>
       </c>
       <c r="G10">
         <v>359.5</v>
@@ -2113,28 +2113,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M10">
-        <v>15.6706632</v>
+        <v>17.6294961</v>
       </c>
       <c r="N10">
-        <v>516.9293367999999</v>
+        <v>514.9705038999999</v>
       </c>
       <c r="O10">
-        <v>155.0788010399999</v>
+        <v>154.49115117</v>
       </c>
       <c r="P10">
-        <v>361.85053576</v>
+        <v>360.47935273</v>
       </c>
       <c r="Q10">
-        <v>586.6505357599999</v>
+        <v>585.27935273</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09101078341465089</v>
+        <v>0.09136711052226951</v>
       </c>
       <c r="T10">
-        <v>1.044128947220575</v>
+        <v>1.05235821067597</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>33.98707465042065</v>
+        <v>30.21073302259614</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08631297057526525</v>
+        <v>0.08607922040905169</v>
       </c>
       <c r="C11">
-        <v>3537.04803085218</v>
+        <v>3518.579080908115</v>
       </c>
       <c r="D11">
-        <v>3528.03503085218</v>
+        <v>3548.509080908114</v>
       </c>
       <c r="E11">
-        <v>-76.91299999999995</v>
+        <v>-37.96999999999997</v>
       </c>
       <c r="F11">
-        <v>350.487</v>
+        <v>389.43</v>
       </c>
       <c r="G11">
         <v>359.5</v>
@@ -2195,28 +2195,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M11">
-        <v>17.6294961</v>
+        <v>19.588329</v>
       </c>
       <c r="N11">
-        <v>514.9705038999999</v>
+        <v>513.0116709999999</v>
       </c>
       <c r="O11">
-        <v>154.49115117</v>
+        <v>153.9035013</v>
       </c>
       <c r="P11">
-        <v>360.47935273</v>
+        <v>359.1081696999999</v>
       </c>
       <c r="Q11">
-        <v>585.27935273</v>
+        <v>583.9081696999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09136711052226951</v>
+        <v>0.09173135601005744</v>
       </c>
       <c r="T11">
-        <v>1.05235821067597</v>
+        <v>1.060770346652597</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.21073302259614</v>
+        <v>27.18965972033653</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08607922040905169</v>
+        <v>0.08584547024283813</v>
       </c>
       <c r="C12">
-        <v>3518.579080908115</v>
+        <v>3500.349149888019</v>
       </c>
       <c r="D12">
-        <v>3548.509080908114</v>
+        <v>3569.222149888019</v>
       </c>
       <c r="E12">
-        <v>-37.96999999999991</v>
+        <v>0.97300000000007</v>
       </c>
       <c r="F12">
-        <v>389.4300000000001</v>
+        <v>428.373</v>
       </c>
       <c r="G12">
         <v>359.5</v>
@@ -2277,28 +2277,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M12">
-        <v>19.588329</v>
+        <v>21.5471619</v>
       </c>
       <c r="N12">
-        <v>513.0116709999999</v>
+        <v>511.0528380999999</v>
       </c>
       <c r="O12">
-        <v>153.9035013</v>
+        <v>153.31585143</v>
       </c>
       <c r="P12">
-        <v>359.1081696999999</v>
+        <v>357.73698667</v>
       </c>
       <c r="Q12">
-        <v>583.9081696999999</v>
+        <v>582.53698667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09173135601005744</v>
+        <v>0.09210378678970577</v>
       </c>
       <c r="T12">
-        <v>1.060770346652597</v>
+        <v>1.069371519392743</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.18965972033653</v>
+        <v>24.7178724730332</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08584547024283813</v>
+        <v>0.08561172007662457</v>
       </c>
       <c r="C13">
-        <v>3500.349149888019</v>
+        <v>3482.362447912412</v>
       </c>
       <c r="D13">
-        <v>3569.222149888019</v>
+        <v>3590.178447912412</v>
       </c>
       <c r="E13">
-        <v>0.97300000000007</v>
+        <v>39.91600000000005</v>
       </c>
       <c r="F13">
-        <v>428.373</v>
+        <v>467.316</v>
       </c>
       <c r="G13">
         <v>359.5</v>
@@ -2359,28 +2359,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M13">
-        <v>21.5471619</v>
+        <v>23.5059948</v>
       </c>
       <c r="N13">
-        <v>511.0528380999999</v>
+        <v>509.0940051999999</v>
       </c>
       <c r="O13">
-        <v>153.31585143</v>
+        <v>152.72820156</v>
       </c>
       <c r="P13">
-        <v>357.73698667</v>
+        <v>356.36580364</v>
       </c>
       <c r="Q13">
-        <v>582.53698667</v>
+        <v>581.1658036399999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09210378678970577</v>
+        <v>0.09248468190525519</v>
       </c>
       <c r="T13">
-        <v>1.069371519392743</v>
+        <v>1.078168173331528</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>24.7178724730332</v>
+        <v>22.65804976694711</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08561172007662457</v>
+        <v>0.08537796991041102</v>
       </c>
       <c r="C14">
-        <v>3482.362447912412</v>
+        <v>3464.623284562837</v>
       </c>
       <c r="D14">
-        <v>3590.178447912412</v>
+        <v>3611.382284562837</v>
       </c>
       <c r="E14">
-        <v>39.91600000000005</v>
+        <v>78.85900000000004</v>
       </c>
       <c r="F14">
-        <v>467.316</v>
+        <v>506.259</v>
       </c>
       <c r="G14">
         <v>359.5</v>
@@ -2441,28 +2441,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M14">
-        <v>23.5059948</v>
+        <v>25.4648277</v>
       </c>
       <c r="N14">
-        <v>509.0940051999999</v>
+        <v>507.1351722999999</v>
       </c>
       <c r="O14">
-        <v>152.72820156</v>
+        <v>152.14055169</v>
       </c>
       <c r="P14">
-        <v>356.36580364</v>
+        <v>354.99462061</v>
       </c>
       <c r="Q14">
-        <v>581.1658036399999</v>
+        <v>579.79462061</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09248468190525519</v>
+        <v>0.09287433323035749</v>
       </c>
       <c r="T14">
-        <v>1.078168173331528</v>
+        <v>1.087167049199942</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>22.65804976694711</v>
+        <v>20.91512286179733</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08537796991041102</v>
+        <v>0.08514421974419745</v>
       </c>
       <c r="C15">
-        <v>3464.623284562837</v>
+        <v>3447.136071836439</v>
       </c>
       <c r="D15">
-        <v>3611.382284562837</v>
+        <v>3632.838071836439</v>
       </c>
       <c r="E15">
-        <v>78.85900000000004</v>
+        <v>117.8020000000001</v>
       </c>
       <c r="F15">
-        <v>506.259</v>
+        <v>545.2020000000001</v>
       </c>
       <c r="G15">
         <v>359.5</v>
@@ -2523,28 +2523,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M15">
-        <v>25.4648277</v>
+        <v>27.42366060000001</v>
       </c>
       <c r="N15">
-        <v>507.1351722999999</v>
+        <v>505.1763393999999</v>
       </c>
       <c r="O15">
-        <v>152.14055169</v>
+        <v>151.55290182</v>
       </c>
       <c r="P15">
-        <v>354.99462061</v>
+        <v>353.62343758</v>
       </c>
       <c r="Q15">
-        <v>579.79462061</v>
+        <v>578.4234375799999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09287433323035749</v>
+        <v>0.09327304621418307</v>
       </c>
       <c r="T15">
-        <v>1.087167049199942</v>
+        <v>1.096375201251341</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.91512286179733</v>
+        <v>19.42118551452609</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08514421974419745</v>
+        <v>0.08491046957798387</v>
       </c>
       <c r="C16">
-        <v>3447.136071836439</v>
+        <v>3429.905327206464</v>
       </c>
       <c r="D16">
-        <v>3632.838071836439</v>
+        <v>3654.550327206464</v>
       </c>
       <c r="E16">
-        <v>117.8020000000001</v>
+        <v>156.7450000000001</v>
       </c>
       <c r="F16">
-        <v>545.2020000000001</v>
+        <v>584.1450000000001</v>
       </c>
       <c r="G16">
         <v>359.5</v>
@@ -2605,28 +2605,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M16">
-        <v>27.42366060000001</v>
+        <v>29.3824935</v>
       </c>
       <c r="N16">
-        <v>505.1763393999999</v>
+        <v>503.2175064999999</v>
       </c>
       <c r="O16">
-        <v>151.55290182</v>
+        <v>150.96525195</v>
       </c>
       <c r="P16">
-        <v>353.62343758</v>
+        <v>352.25225455</v>
       </c>
       <c r="Q16">
-        <v>578.4234375799999</v>
+        <v>577.05225455</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09327304621418307</v>
+        <v>0.09368114067998104</v>
       </c>
       <c r="T16">
-        <v>1.096375201251341</v>
+        <v>1.10580001570395</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.42118551452609</v>
+        <v>18.12643981355768</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08491046957798387</v>
+        <v>0.08467671941177031</v>
       </c>
       <c r="C17">
-        <v>3429.905327206464</v>
+        <v>3412.935676793201</v>
       </c>
       <c r="D17">
-        <v>3654.550327206464</v>
+        <v>3676.523676793201</v>
       </c>
       <c r="E17">
-        <v>156.745</v>
+        <v>195.6880000000001</v>
       </c>
       <c r="F17">
-        <v>584.145</v>
+        <v>623.0880000000001</v>
       </c>
       <c r="G17">
         <v>359.5</v>
@@ -2687,28 +2687,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M17">
-        <v>29.3824935</v>
+        <v>31.3413264</v>
       </c>
       <c r="N17">
-        <v>503.2175064999999</v>
+        <v>501.2586735999999</v>
       </c>
       <c r="O17">
-        <v>150.96525195</v>
+        <v>150.37760208</v>
       </c>
       <c r="P17">
-        <v>352.25225455</v>
+        <v>350.8810715199999</v>
       </c>
       <c r="Q17">
-        <v>577.05225455</v>
+        <v>575.6810715199999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09368114067998104</v>
+        <v>0.09409895168067894</v>
       </c>
       <c r="T17">
-        <v>1.10580001570395</v>
+        <v>1.115449230500668</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.12643981355768</v>
+        <v>16.99353732521033</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08467671941177031</v>
+        <v>0.08444296924555675</v>
       </c>
       <c r="C18">
-        <v>3412.935676793201</v>
+        <v>3396.231858649997</v>
       </c>
       <c r="D18">
-        <v>3676.523676793201</v>
+        <v>3698.762858649997</v>
       </c>
       <c r="E18">
-        <v>195.6880000000001</v>
+        <v>234.6310000000001</v>
       </c>
       <c r="F18">
-        <v>623.0880000000001</v>
+        <v>662.0310000000001</v>
       </c>
       <c r="G18">
         <v>359.5</v>
@@ -2769,28 +2769,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M18">
-        <v>31.3413264</v>
+        <v>33.3001593</v>
       </c>
       <c r="N18">
-        <v>501.2586735999999</v>
+        <v>499.2998406999999</v>
       </c>
       <c r="O18">
-        <v>150.37760208</v>
+        <v>149.78995221</v>
       </c>
       <c r="P18">
-        <v>350.8810715199999</v>
+        <v>349.5098884899999</v>
       </c>
       <c r="Q18">
-        <v>575.6810715199999</v>
+        <v>574.3098884899999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09409895168067894</v>
+        <v>0.09452683041633345</v>
       </c>
       <c r="T18">
-        <v>1.115449230500668</v>
+        <v>1.125330956497308</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.99353732521033</v>
+        <v>15.9939174825509</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08444296924555675</v>
+        <v>0.0842092190793432</v>
       </c>
       <c r="C19">
-        <v>3396.231858649997</v>
+        <v>3379.798726169249</v>
       </c>
       <c r="D19">
-        <v>3698.762858649997</v>
+        <v>3721.272726169249</v>
       </c>
       <c r="E19">
-        <v>234.6310000000001</v>
+        <v>273.5740000000002</v>
       </c>
       <c r="F19">
-        <v>662.0310000000001</v>
+        <v>700.9740000000002</v>
       </c>
       <c r="G19">
         <v>359.5</v>
@@ -2851,28 +2851,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M19">
-        <v>33.3001593</v>
+        <v>35.25899220000001</v>
       </c>
       <c r="N19">
-        <v>499.2998406999999</v>
+        <v>497.3410077999999</v>
       </c>
       <c r="O19">
-        <v>149.78995221</v>
+        <v>149.20230234</v>
       </c>
       <c r="P19">
-        <v>349.5098884899999</v>
+        <v>348.1387054599999</v>
       </c>
       <c r="Q19">
-        <v>574.3098884899999</v>
+        <v>572.9387054599999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09452683041633345</v>
+        <v>0.09496514521871122</v>
       </c>
       <c r="T19">
-        <v>1.125330956497308</v>
+        <v>1.135453700201183</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.9939174825509</v>
+        <v>15.10536651129807</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08420921907934321</v>
+        <v>0.08397546891312964</v>
       </c>
       <c r="C20">
-        <v>3379.798726169247</v>
+        <v>3363.641251613546</v>
       </c>
       <c r="D20">
-        <v>3721.272726169248</v>
+        <v>3744.058251613545</v>
       </c>
       <c r="E20">
-        <v>273.5740000000001</v>
+        <v>312.5170000000001</v>
       </c>
       <c r="F20">
-        <v>700.974</v>
+        <v>739.917</v>
       </c>
       <c r="G20">
         <v>359.5</v>
@@ -2933,28 +2933,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M20">
-        <v>35.2589922</v>
+        <v>37.2178251</v>
       </c>
       <c r="N20">
-        <v>497.3410077999999</v>
+        <v>495.3821748999999</v>
       </c>
       <c r="O20">
-        <v>149.20230234</v>
+        <v>148.61465247</v>
       </c>
       <c r="P20">
-        <v>348.1387054599999</v>
+        <v>346.7675224299999</v>
       </c>
       <c r="Q20">
-        <v>572.9387054599999</v>
+        <v>571.5675224299999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09496514521871122</v>
+        <v>0.09541428260880203</v>
       </c>
       <c r="T20">
-        <v>1.135453700201183</v>
+        <v>1.145826388194042</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.10536651129807</v>
+        <v>14.31034722122975</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08397546891312964</v>
+        <v>0.08374171874691608</v>
       </c>
       <c r="C21">
-        <v>3363.641251613546</v>
+        <v>3347.764529777316</v>
       </c>
       <c r="D21">
-        <v>3744.058251613545</v>
+        <v>3767.124529777316</v>
       </c>
       <c r="E21">
-        <v>312.5170000000001</v>
+        <v>351.4600000000002</v>
       </c>
       <c r="F21">
-        <v>739.917</v>
+        <v>778.8600000000001</v>
       </c>
       <c r="G21">
         <v>359.5</v>
@@ -3015,28 +3015,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M21">
-        <v>37.2178251</v>
+        <v>39.176658</v>
       </c>
       <c r="N21">
-        <v>495.3821748999999</v>
+        <v>493.4233419999999</v>
       </c>
       <c r="O21">
-        <v>148.61465247</v>
+        <v>148.0270026</v>
       </c>
       <c r="P21">
-        <v>346.7675224299999</v>
+        <v>345.3963394</v>
       </c>
       <c r="Q21">
-        <v>571.5675224299999</v>
+        <v>570.1963393999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09541428260880203</v>
+        <v>0.0958746484336451</v>
       </c>
       <c r="T21">
-        <v>1.145826388194042</v>
+        <v>1.156458393386723</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.31034722122975</v>
+        <v>13.59482986016826</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08374171874691608</v>
+        <v>0.08350796858070252</v>
       </c>
       <c r="C22">
-        <v>3347.764529777316</v>
+        <v>3332.173781784688</v>
       </c>
       <c r="D22">
-        <v>3767.124529777316</v>
+        <v>3790.476781784688</v>
       </c>
       <c r="E22">
-        <v>351.4600000000002</v>
+        <v>390.4030000000001</v>
       </c>
       <c r="F22">
-        <v>778.8600000000001</v>
+        <v>817.8030000000001</v>
       </c>
       <c r="G22">
         <v>359.5</v>
@@ -3097,28 +3097,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M22">
-        <v>39.176658</v>
+        <v>41.1354909</v>
       </c>
       <c r="N22">
-        <v>493.4233419999999</v>
+        <v>491.4645090999999</v>
       </c>
       <c r="O22">
-        <v>148.0270026</v>
+        <v>147.43935273</v>
       </c>
       <c r="P22">
-        <v>345.3963394</v>
+        <v>344.02515637</v>
       </c>
       <c r="Q22">
-        <v>570.1963393999999</v>
+        <v>568.8251563700001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0958746484336451</v>
+        <v>0.09634666908949685</v>
       </c>
       <c r="T22">
-        <v>1.156458393386723</v>
+        <v>1.167359563267826</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.59482986016826</v>
+        <v>12.94745700968406</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08350796858070252</v>
+        <v>0.08350521841448896</v>
       </c>
       <c r="C23">
-        <v>3332.173781784688</v>
+        <v>3293.507253891649</v>
       </c>
       <c r="D23">
-        <v>3790.476781784688</v>
+        <v>3790.75325389165</v>
       </c>
       <c r="E23">
-        <v>390.403</v>
+        <v>429.3460000000001</v>
       </c>
       <c r="F23">
-        <v>817.803</v>
+        <v>856.7460000000001</v>
       </c>
       <c r="G23">
         <v>359.5</v>
@@ -3179,45 +3179,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M23">
-        <v>41.1354909</v>
+        <v>44.37944280000001</v>
       </c>
       <c r="N23">
-        <v>491.4645090999999</v>
+        <v>488.2205571999999</v>
       </c>
       <c r="O23">
-        <v>147.43935273</v>
+        <v>146.46616716</v>
       </c>
       <c r="P23">
-        <v>344.02515637</v>
+        <v>341.75439004</v>
       </c>
       <c r="Q23">
-        <v>568.8251563700001</v>
+        <v>566.55439004</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09634666908949685</v>
+        <v>0.09683079283908841</v>
       </c>
       <c r="T23">
-        <v>1.167359563267825</v>
+        <v>1.178540250325367</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>12.94745700968406</v>
+        <v>12.00105198256342</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08350521841448896</v>
+        <v>0.08328196824827538</v>
       </c>
       <c r="C24">
-        <v>3293.507253891649</v>
+        <v>3277.142745191793</v>
       </c>
       <c r="D24">
-        <v>3790.75325389165</v>
+        <v>3813.331745191794</v>
       </c>
       <c r="E24">
-        <v>429.3460000000001</v>
+        <v>468.2890000000001</v>
       </c>
       <c r="F24">
-        <v>856.7460000000001</v>
+        <v>895.6890000000001</v>
       </c>
       <c r="G24">
         <v>359.5</v>
@@ -3261,28 +3261,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M24">
-        <v>44.37944280000001</v>
+        <v>46.3966902</v>
       </c>
       <c r="N24">
-        <v>488.2205571999999</v>
+        <v>486.2033097999999</v>
       </c>
       <c r="O24">
-        <v>146.46616716</v>
+        <v>145.86099294</v>
       </c>
       <c r="P24">
-        <v>341.75439004</v>
+        <v>340.3423168599999</v>
       </c>
       <c r="Q24">
-        <v>566.55439004</v>
+        <v>565.1423168599999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09683079283908841</v>
+        <v>0.09732749123152648</v>
       </c>
       <c r="T24">
-        <v>1.178540250325367</v>
+        <v>1.190011344838948</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.00105198256342</v>
+        <v>11.47926711375631</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08328196824827538</v>
+        <v>0.08305871808206183</v>
       </c>
       <c r="C25">
-        <v>3277.142745191793</v>
+        <v>3261.048812195829</v>
       </c>
       <c r="D25">
-        <v>3813.331745191794</v>
+        <v>3836.18081219583</v>
       </c>
       <c r="E25">
-        <v>468.2890000000001</v>
+        <v>507.2320000000001</v>
       </c>
       <c r="F25">
-        <v>895.6890000000001</v>
+        <v>934.6320000000001</v>
       </c>
       <c r="G25">
         <v>359.5</v>
@@ -3343,28 +3343,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M25">
-        <v>46.3966902</v>
+        <v>48.4139376</v>
       </c>
       <c r="N25">
-        <v>486.2033097999999</v>
+        <v>484.1860623999999</v>
       </c>
       <c r="O25">
-        <v>145.86099294</v>
+        <v>145.25581872</v>
       </c>
       <c r="P25">
-        <v>340.3423168599999</v>
+        <v>338.9302436799999</v>
       </c>
       <c r="Q25">
-        <v>565.1423168599999</v>
+        <v>563.7302436799999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09732749123152648</v>
+        <v>0.09783726063429188</v>
       </c>
       <c r="T25">
-        <v>1.190011344838948</v>
+        <v>1.201784310260782</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.47926711375631</v>
+        <v>11.0009643173498</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08305871808206183</v>
+        <v>0.08283546791584827</v>
       </c>
       <c r="C26">
-        <v>3261.048812195829</v>
+        <v>3245.230348002801</v>
       </c>
       <c r="D26">
-        <v>3836.18081219583</v>
+        <v>3859.305348002802</v>
       </c>
       <c r="E26">
-        <v>507.2320000000001</v>
+        <v>546.1750000000001</v>
       </c>
       <c r="F26">
-        <v>934.6320000000001</v>
+        <v>973.575</v>
       </c>
       <c r="G26">
         <v>359.5</v>
@@ -3425,28 +3425,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M26">
-        <v>48.4139376</v>
+        <v>50.431185</v>
       </c>
       <c r="N26">
-        <v>484.1860623999999</v>
+        <v>482.1688149999999</v>
       </c>
       <c r="O26">
-        <v>145.25581872</v>
+        <v>144.6506445</v>
       </c>
       <c r="P26">
-        <v>338.9302436799999</v>
+        <v>337.5181704999999</v>
       </c>
       <c r="Q26">
-        <v>563.7302436799999</v>
+        <v>562.3181705</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09783726063429188</v>
+        <v>0.09836062388779769</v>
       </c>
       <c r="T26">
-        <v>1.201784310260782</v>
+        <v>1.213871221427198</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.0009643173498</v>
+        <v>10.56092574465581</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08283546791584827</v>
+        <v>0.08261221774963469</v>
       </c>
       <c r="C27">
-        <v>3245.230348002801</v>
+        <v>3229.692364409865</v>
       </c>
       <c r="D27">
-        <v>3859.305348002802</v>
+        <v>3882.710364409865</v>
       </c>
       <c r="E27">
-        <v>546.1750000000001</v>
+        <v>585.1180000000001</v>
       </c>
       <c r="F27">
-        <v>973.575</v>
+        <v>1012.518</v>
       </c>
       <c r="G27">
         <v>359.5</v>
@@ -3507,28 +3507,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M27">
-        <v>50.431185</v>
+        <v>52.4484324</v>
       </c>
       <c r="N27">
-        <v>482.1688149999999</v>
+        <v>480.1515675999999</v>
       </c>
       <c r="O27">
-        <v>144.6506445</v>
+        <v>144.04547028</v>
       </c>
       <c r="P27">
-        <v>337.5181704999999</v>
+        <v>336.1060973199999</v>
       </c>
       <c r="Q27">
-        <v>562.3181705</v>
+        <v>560.90609732</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09836062388779769</v>
+        <v>0.09889813209410095</v>
       </c>
       <c r="T27">
-        <v>1.213871221427198</v>
+        <v>1.226284805868382</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.56092574465581</v>
+        <v>10.15473629293828</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08261221774963469</v>
+        <v>0.08271026758342113</v>
       </c>
       <c r="C28">
-        <v>3229.692364409865</v>
+        <v>3180.435185434845</v>
       </c>
       <c r="D28">
-        <v>3882.710364409865</v>
+        <v>3872.396185434845</v>
       </c>
       <c r="E28">
-        <v>585.1180000000001</v>
+        <v>624.061</v>
       </c>
       <c r="F28">
-        <v>1012.518</v>
+        <v>1051.461</v>
       </c>
       <c r="G28">
         <v>359.5</v>
@@ -3589,45 +3589,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M28">
-        <v>52.4484324</v>
+        <v>56.2531635</v>
       </c>
       <c r="N28">
-        <v>480.1515675999999</v>
+        <v>476.3468364999999</v>
       </c>
       <c r="O28">
-        <v>144.04547028</v>
+        <v>142.90405095</v>
       </c>
       <c r="P28">
-        <v>336.1060973199999</v>
+        <v>333.4427855499999</v>
       </c>
       <c r="Q28">
-        <v>560.90609732</v>
+        <v>558.24278555</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09889813209410095</v>
+        <v>0.0994503665526317</v>
       </c>
       <c r="T28">
-        <v>1.226284805868382</v>
+        <v>1.239038488513434</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>10.15473629293828</v>
+        <v>9.467911969075301</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08271026758342113</v>
+        <v>0.08249891741720757</v>
       </c>
       <c r="C29">
-        <v>3180.435185434845</v>
+        <v>3163.793431221802</v>
       </c>
       <c r="D29">
-        <v>3872.396185434845</v>
+        <v>3894.697431221803</v>
       </c>
       <c r="E29">
-        <v>624.061</v>
+        <v>663.0040000000002</v>
       </c>
       <c r="F29">
-        <v>1051.461</v>
+        <v>1090.404</v>
       </c>
       <c r="G29">
         <v>359.5</v>
@@ -3671,28 +3671,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M29">
-        <v>56.2531635</v>
+        <v>58.33661400000001</v>
       </c>
       <c r="N29">
-        <v>476.3468364999999</v>
+        <v>474.2633859999999</v>
       </c>
       <c r="O29">
-        <v>142.90405095</v>
+        <v>142.2790158</v>
       </c>
       <c r="P29">
-        <v>333.4427855499999</v>
+        <v>331.9843701999999</v>
       </c>
       <c r="Q29">
-        <v>558.24278555</v>
+        <v>556.7843702</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0994503665526317</v>
+        <v>0.1000179408572327</v>
       </c>
       <c r="T29">
-        <v>1.239038488513434</v>
+        <v>1.252146440120848</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.467911969075301</v>
+        <v>9.129772255894039</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08249891741720757</v>
+        <v>0.08228756725099401</v>
       </c>
       <c r="C30">
-        <v>3163.793431221802</v>
+        <v>3147.410031969584</v>
       </c>
       <c r="D30">
-        <v>3894.697431221803</v>
+        <v>3917.257031969585</v>
       </c>
       <c r="E30">
-        <v>663.0040000000002</v>
+        <v>701.9470000000002</v>
       </c>
       <c r="F30">
-        <v>1090.404</v>
+        <v>1129.347</v>
       </c>
       <c r="G30">
         <v>359.5</v>
@@ -3753,28 +3753,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M30">
-        <v>58.33661400000001</v>
+        <v>60.42006450000001</v>
       </c>
       <c r="N30">
-        <v>474.2633859999999</v>
+        <v>472.1799354999999</v>
       </c>
       <c r="O30">
-        <v>142.2790158</v>
+        <v>141.65398065</v>
       </c>
       <c r="P30">
-        <v>331.9843701999999</v>
+        <v>330.5259548499999</v>
       </c>
       <c r="Q30">
-        <v>556.7843702</v>
+        <v>555.32595485</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1000179408572327</v>
+        <v>0.1006015031704141</v>
       </c>
       <c r="T30">
-        <v>1.252146440120848</v>
+        <v>1.265623629801711</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.129772255894039</v>
+        <v>8.814952522932177</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08228756725099401</v>
+        <v>0.08207621708478044</v>
       </c>
       <c r="C31">
-        <v>3147.410031969584</v>
+        <v>3131.289503311433</v>
       </c>
       <c r="D31">
-        <v>3917.257031969585</v>
+        <v>3940.079503311433</v>
       </c>
       <c r="E31">
-        <v>701.947</v>
+        <v>740.89</v>
       </c>
       <c r="F31">
-        <v>1129.347</v>
+        <v>1168.29</v>
       </c>
       <c r="G31">
         <v>359.5</v>
@@ -3835,28 +3835,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M31">
-        <v>60.4200645</v>
+        <v>62.503515</v>
       </c>
       <c r="N31">
-        <v>472.1799354999999</v>
+        <v>470.0964849999999</v>
       </c>
       <c r="O31">
-        <v>141.65398065</v>
+        <v>141.0289455</v>
       </c>
       <c r="P31">
-        <v>330.5259548499999</v>
+        <v>329.0675395</v>
       </c>
       <c r="Q31">
-        <v>555.32595485</v>
+        <v>553.8675395</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1006015031704141</v>
+        <v>0.1012017386925435</v>
       </c>
       <c r="T31">
-        <v>1.265623629801711</v>
+        <v>1.279485882044885</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.814952522932179</v>
+        <v>8.521120772167773</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08207621708478044</v>
+        <v>0.08186486691856688</v>
       </c>
       <c r="C32">
-        <v>3131.289503311433</v>
+        <v>3115.43646673206</v>
       </c>
       <c r="D32">
-        <v>3940.079503311433</v>
+        <v>3963.16946673206</v>
       </c>
       <c r="E32">
-        <v>740.89</v>
+        <v>779.833</v>
       </c>
       <c r="F32">
-        <v>1168.29</v>
+        <v>1207.233</v>
       </c>
       <c r="G32">
         <v>359.5</v>
@@ -3917,28 +3917,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M32">
-        <v>62.503515</v>
+        <v>64.58696549999999</v>
       </c>
       <c r="N32">
-        <v>470.0964849999999</v>
+        <v>468.0130344999999</v>
       </c>
       <c r="O32">
-        <v>141.0289455</v>
+        <v>140.40391035</v>
       </c>
       <c r="P32">
-        <v>329.0675395</v>
+        <v>327.60912415</v>
       </c>
       <c r="Q32">
-        <v>553.8675395</v>
+        <v>552.40912415</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1012017386925435</v>
+        <v>0.1018193723457491</v>
       </c>
       <c r="T32">
-        <v>1.279485882044885</v>
+        <v>1.293749938700903</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.521120772167773</v>
+        <v>8.246245908549458</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08186486691856688</v>
+        <v>0.08165351675235331</v>
       </c>
       <c r="C33">
-        <v>3115.43646673206</v>
+        <v>3099.855652687539</v>
       </c>
       <c r="D33">
-        <v>3963.16946673206</v>
+        <v>3986.531652687539</v>
       </c>
       <c r="E33">
-        <v>779.833</v>
+        <v>818.7760000000002</v>
       </c>
       <c r="F33">
-        <v>1207.233</v>
+        <v>1246.176</v>
       </c>
       <c r="G33">
         <v>359.5</v>
@@ -3999,28 +3999,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M33">
-        <v>64.58696549999999</v>
+        <v>66.670416</v>
       </c>
       <c r="N33">
-        <v>468.0130344999999</v>
+        <v>465.9295839999999</v>
       </c>
       <c r="O33">
-        <v>140.40391035</v>
+        <v>139.7788752</v>
       </c>
       <c r="P33">
-        <v>327.60912415</v>
+        <v>326.1507088</v>
       </c>
       <c r="Q33">
-        <v>552.40912415</v>
+        <v>550.9507088</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1018193723457491</v>
+        <v>0.1024551716946372</v>
       </c>
       <c r="T33">
-        <v>1.293749938700903</v>
+        <v>1.30843352643504</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.246245908549458</v>
+        <v>7.988550723907286</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08165351675235331</v>
+        <v>0.08144216658613976</v>
       </c>
       <c r="C34">
-        <v>3099.855652687539</v>
+        <v>3084.551903836169</v>
       </c>
       <c r="D34">
-        <v>3986.531652687539</v>
+        <v>4010.17090383617</v>
       </c>
       <c r="E34">
-        <v>818.7760000000002</v>
+        <v>857.7190000000002</v>
       </c>
       <c r="F34">
-        <v>1246.176</v>
+        <v>1285.119</v>
       </c>
       <c r="G34">
         <v>359.5</v>
@@ -4081,28 +4081,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M34">
-        <v>66.670416</v>
+        <v>68.7538665</v>
       </c>
       <c r="N34">
-        <v>465.9295839999999</v>
+        <v>463.8461334999999</v>
       </c>
       <c r="O34">
-        <v>139.7788752</v>
+        <v>139.15384005</v>
       </c>
       <c r="P34">
-        <v>326.1507088</v>
+        <v>324.69229345</v>
       </c>
       <c r="Q34">
-        <v>550.9507088</v>
+        <v>549.49229345</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1024551716946372</v>
+        <v>0.1031099501285668</v>
       </c>
       <c r="T34">
-        <v>1.30843352643504</v>
+        <v>1.323555430220943</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.988550723907286</v>
+        <v>7.746473429243428</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08144216658613976</v>
+        <v>0.0814212164199262</v>
       </c>
       <c r="C35">
-        <v>3084.551903836169</v>
+        <v>3047.967434942738</v>
       </c>
       <c r="D35">
-        <v>4010.17090383617</v>
+        <v>4012.529434942738</v>
       </c>
       <c r="E35">
-        <v>857.7190000000002</v>
+        <v>896.6620000000001</v>
       </c>
       <c r="F35">
-        <v>1285.119</v>
+        <v>1324.062</v>
       </c>
       <c r="G35">
         <v>359.5</v>
@@ -4163,45 +4163,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M35">
-        <v>68.7538665</v>
+        <v>71.89656660000001</v>
       </c>
       <c r="N35">
-        <v>463.8461334999999</v>
+        <v>460.7034333999999</v>
       </c>
       <c r="O35">
-        <v>139.15384005</v>
+        <v>138.21103002</v>
       </c>
       <c r="P35">
-        <v>324.69229345</v>
+        <v>322.4924033799999</v>
       </c>
       <c r="Q35">
-        <v>549.49229345</v>
+        <v>547.29240338</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1031099501285668</v>
+        <v>0.1037845703332215</v>
       </c>
       <c r="T35">
-        <v>1.323555430220943</v>
+        <v>1.339135573515509</v>
       </c>
       <c r="U35">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y35">
-        <v>7.746473429243428</v>
+        <v>7.407864174698988</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0814212164199262</v>
+        <v>0.08121546625371263</v>
       </c>
       <c r="C36">
-        <v>3047.967434942738</v>
+        <v>3032.335679591104</v>
       </c>
       <c r="D36">
-        <v>4012.529434942738</v>
+        <v>4035.840679591104</v>
       </c>
       <c r="E36">
-        <v>896.6620000000001</v>
+        <v>935.6050000000001</v>
       </c>
       <c r="F36">
-        <v>1324.062</v>
+        <v>1363.005</v>
       </c>
       <c r="G36">
         <v>359.5</v>
@@ -4245,28 +4245,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M36">
-        <v>71.89656660000001</v>
+        <v>74.0111715</v>
       </c>
       <c r="N36">
-        <v>460.7034333999999</v>
+        <v>458.5888284999999</v>
       </c>
       <c r="O36">
-        <v>138.21103002</v>
+        <v>137.57664855</v>
       </c>
       <c r="P36">
-        <v>322.4924033799999</v>
+        <v>321.01217995</v>
       </c>
       <c r="Q36">
-        <v>547.29240338</v>
+        <v>545.81217995</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1037845703332215</v>
+        <v>0.1044799480826348</v>
       </c>
       <c r="T36">
-        <v>1.339135573515509</v>
+        <v>1.355195105834523</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.407864174698988</v>
+        <v>7.196210912564732</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08121546625371263</v>
+        <v>0.08100971608749907</v>
       </c>
       <c r="C37">
-        <v>3032.335679591104</v>
+        <v>3016.976365655875</v>
       </c>
       <c r="D37">
-        <v>4035.840679591104</v>
+        <v>4059.424365655876</v>
       </c>
       <c r="E37">
-        <v>935.6050000000001</v>
+        <v>974.5480000000003</v>
       </c>
       <c r="F37">
-        <v>1363.005</v>
+        <v>1401.948</v>
       </c>
       <c r="G37">
         <v>359.5</v>
@@ -4327,28 +4327,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M37">
-        <v>74.0111715</v>
+        <v>76.12577640000002</v>
       </c>
       <c r="N37">
-        <v>458.5888284999999</v>
+        <v>456.4742235999999</v>
       </c>
       <c r="O37">
-        <v>137.57664855</v>
+        <v>136.94226708</v>
       </c>
       <c r="P37">
-        <v>321.01217995</v>
+        <v>319.5319565199999</v>
       </c>
       <c r="Q37">
-        <v>545.81217995</v>
+        <v>544.3319565199999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1044799480826348</v>
+        <v>0.1051970563867173</v>
       </c>
       <c r="T37">
-        <v>1.355195105834523</v>
+        <v>1.371756498538506</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.196210912564732</v>
+        <v>6.996316164993488</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08100971608749907</v>
+        <v>0.08080396592128553</v>
       </c>
       <c r="C38">
-        <v>3016.976365655875</v>
+        <v>3001.894297295542</v>
       </c>
       <c r="D38">
-        <v>4059.424365655876</v>
+        <v>4083.285297295543</v>
       </c>
       <c r="E38">
-        <v>974.5480000000001</v>
+        <v>1013.491</v>
       </c>
       <c r="F38">
-        <v>1401.948</v>
+        <v>1440.891</v>
       </c>
       <c r="G38">
         <v>359.5</v>
@@ -4409,28 +4409,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M38">
-        <v>76.12577640000001</v>
+        <v>78.24038130000001</v>
       </c>
       <c r="N38">
-        <v>456.4742235999999</v>
+        <v>454.3596186999999</v>
       </c>
       <c r="O38">
-        <v>136.94226708</v>
+        <v>136.30788561</v>
       </c>
       <c r="P38">
-        <v>319.5319565199999</v>
+        <v>318.0517330899999</v>
       </c>
       <c r="Q38">
-        <v>544.3319565199999</v>
+        <v>542.8517330899999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1051970563867173</v>
+        <v>0.1059369300337865</v>
       </c>
       <c r="T38">
-        <v>1.371756498538506</v>
+        <v>1.388843649741028</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.996316164993489</v>
+        <v>6.807226538912584</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08080396592128553</v>
+        <v>0.08059821575507195</v>
       </c>
       <c r="C39">
-        <v>3001.894297295542</v>
+        <v>2987.094392290106</v>
       </c>
       <c r="D39">
-        <v>4083.285297295543</v>
+        <v>4107.428392290106</v>
       </c>
       <c r="E39">
-        <v>1013.491</v>
+        <v>1052.434</v>
       </c>
       <c r="F39">
-        <v>1440.891</v>
+        <v>1479.834</v>
       </c>
       <c r="G39">
         <v>359.5</v>
@@ -4491,28 +4491,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M39">
-        <v>78.24038130000001</v>
+        <v>80.3549862</v>
       </c>
       <c r="N39">
-        <v>454.3596186999999</v>
+        <v>452.2450137999999</v>
       </c>
       <c r="O39">
-        <v>136.30788561</v>
+        <v>135.67350414</v>
       </c>
       <c r="P39">
-        <v>318.0517330899999</v>
+        <v>316.5715096599999</v>
       </c>
       <c r="Q39">
-        <v>542.8517330899999</v>
+        <v>541.3715096599999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1059369300337865</v>
+        <v>0.1067006705726967</v>
       </c>
       <c r="T39">
-        <v>1.388843649741028</v>
+        <v>1.406481999369439</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.807226538912584</v>
+        <v>6.628088998414885</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08059821575507195</v>
+        <v>0.08039246558885839</v>
       </c>
       <c r="C40">
-        <v>2987.094392290106</v>
+        <v>2972.581685420069</v>
       </c>
       <c r="D40">
-        <v>4107.428392290106</v>
+        <v>4131.858685420069</v>
       </c>
       <c r="E40">
-        <v>1052.434</v>
+        <v>1091.377</v>
       </c>
       <c r="F40">
-        <v>1479.834</v>
+        <v>1518.777</v>
       </c>
       <c r="G40">
         <v>359.5</v>
@@ -4573,28 +4573,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M40">
-        <v>80.3549862</v>
+        <v>82.4695911</v>
       </c>
       <c r="N40">
-        <v>452.2450137999999</v>
+        <v>450.1304088999999</v>
       </c>
       <c r="O40">
-        <v>135.67350414</v>
+        <v>135.03912267</v>
       </c>
       <c r="P40">
-        <v>316.5715096599999</v>
+        <v>315.0912862299999</v>
       </c>
       <c r="Q40">
-        <v>541.3715096599999</v>
+        <v>539.8912862299999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1067006705726967</v>
+        <v>0.1074894517850138</v>
       </c>
       <c r="T40">
-        <v>1.406481999369439</v>
+        <v>1.424698655543043</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.628088998414885</v>
+        <v>6.458137998455529</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08039246558885839</v>
+        <v>0.08018671542264484</v>
       </c>
       <c r="C41">
-        <v>2972.581685420069</v>
+        <v>2958.36133196677</v>
       </c>
       <c r="D41">
-        <v>4131.858685420069</v>
+        <v>4156.58133196677</v>
       </c>
       <c r="E41">
-        <v>1091.377</v>
+        <v>1130.32</v>
       </c>
       <c r="F41">
-        <v>1518.777</v>
+        <v>1557.72</v>
       </c>
       <c r="G41">
         <v>359.5</v>
@@ -4655,28 +4655,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M41">
-        <v>82.4695911</v>
+        <v>84.58419600000002</v>
       </c>
       <c r="N41">
-        <v>450.1304088999999</v>
+        <v>448.0158039999999</v>
       </c>
       <c r="O41">
-        <v>135.03912267</v>
+        <v>134.4047412</v>
       </c>
       <c r="P41">
-        <v>315.0912862299999</v>
+        <v>313.6110627999999</v>
       </c>
       <c r="Q41">
-        <v>539.8912862299999</v>
+        <v>538.4110627999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1074894517850138</v>
+        <v>0.1083045257044081</v>
       </c>
       <c r="T41">
-        <v>1.424698655543043</v>
+        <v>1.443522533589101</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.458137998455529</v>
+        <v>6.296684548494139</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08018671542264484</v>
+        <v>0.07998096525643127</v>
       </c>
       <c r="C42">
-        <v>2958.36133196677</v>
+        <v>2944.438611339118</v>
       </c>
       <c r="D42">
-        <v>4156.58133196677</v>
+        <v>4181.601611339119</v>
       </c>
       <c r="E42">
-        <v>1130.32</v>
+        <v>1169.263</v>
       </c>
       <c r="F42">
-        <v>1557.72</v>
+        <v>1596.663</v>
       </c>
       <c r="G42">
         <v>359.5</v>
@@ -4737,28 +4737,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M42">
-        <v>84.58419600000002</v>
+        <v>86.69880090000001</v>
       </c>
       <c r="N42">
-        <v>448.0158039999999</v>
+        <v>445.9011990999999</v>
       </c>
       <c r="O42">
-        <v>134.4047412</v>
+        <v>133.77035973</v>
       </c>
       <c r="P42">
-        <v>313.6110627999999</v>
+        <v>312.1308393699999</v>
       </c>
       <c r="Q42">
-        <v>538.4110627999999</v>
+        <v>536.9308393699998</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1083045257044081</v>
+        <v>0.1091472292481886</v>
       </c>
       <c r="T42">
-        <v>1.443522533589101</v>
+        <v>1.462984509196041</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.296684548494139</v>
+        <v>6.143106876579648</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07998096525643127</v>
+        <v>0.08006921509021771</v>
       </c>
       <c r="C43">
-        <v>2944.438611339118</v>
+        <v>2894.727181242593</v>
       </c>
       <c r="D43">
-        <v>4181.601611339119</v>
+        <v>4170.833181242593</v>
       </c>
       <c r="E43">
-        <v>1169.263</v>
+        <v>1208.206</v>
       </c>
       <c r="F43">
-        <v>1596.663</v>
+        <v>1635.606</v>
       </c>
       <c r="G43">
         <v>359.5</v>
@@ -4819,45 +4819,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M43">
-        <v>86.69880090000001</v>
+        <v>90.44901180000002</v>
       </c>
       <c r="N43">
-        <v>445.9011990999999</v>
+        <v>442.1509881999999</v>
       </c>
       <c r="O43">
-        <v>133.77035973</v>
+        <v>132.64529646</v>
       </c>
       <c r="P43">
-        <v>312.1308393699999</v>
+        <v>309.50569174</v>
       </c>
       <c r="Q43">
-        <v>536.9308393699998</v>
+        <v>534.3056917399999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1091472292481886</v>
+        <v>0.1100189915348581</v>
       </c>
       <c r="T43">
-        <v>1.462984509196041</v>
+        <v>1.483117587410118</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.143106876579648</v>
+        <v>5.888400430263184</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08006921509021771</v>
+        <v>0.07987046492400415</v>
       </c>
       <c r="C44">
-        <v>2894.727181242593</v>
+        <v>2880.114749958635</v>
       </c>
       <c r="D44">
-        <v>4170.833181242593</v>
+        <v>4195.163749958635</v>
       </c>
       <c r="E44">
-        <v>1208.206</v>
+        <v>1247.149</v>
       </c>
       <c r="F44">
-        <v>1635.606</v>
+        <v>1674.549</v>
       </c>
       <c r="G44">
         <v>359.5</v>
@@ -4901,28 +4901,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M44">
-        <v>90.44901180000001</v>
+        <v>92.6025597</v>
       </c>
       <c r="N44">
-        <v>442.1509881999999</v>
+        <v>439.9974402999999</v>
       </c>
       <c r="O44">
-        <v>132.64529646</v>
+        <v>131.99923209</v>
       </c>
       <c r="P44">
-        <v>309.50569174</v>
+        <v>307.9982082099999</v>
       </c>
       <c r="Q44">
-        <v>534.3056917399999</v>
+        <v>532.79820821</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1100189915348581</v>
+        <v>0.1109213419719371</v>
       </c>
       <c r="T44">
-        <v>1.483117587410118</v>
+        <v>1.50395708942118</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.888400430263185</v>
+        <v>5.751460885373343</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07987046492400415</v>
+        <v>0.0796717147577906</v>
       </c>
       <c r="C45">
-        <v>2880.114749958635</v>
+        <v>2865.787849219024</v>
       </c>
       <c r="D45">
-        <v>4195.163749958635</v>
+        <v>4219.779849219024</v>
       </c>
       <c r="E45">
-        <v>1247.149</v>
+        <v>1286.092</v>
       </c>
       <c r="F45">
-        <v>1674.549</v>
+        <v>1713.492</v>
       </c>
       <c r="G45">
         <v>359.5</v>
@@ -4983,28 +4983,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M45">
-        <v>92.6025597</v>
+        <v>94.75610760000001</v>
       </c>
       <c r="N45">
-        <v>439.9974402999999</v>
+        <v>437.8438923999999</v>
       </c>
       <c r="O45">
-        <v>131.99923209</v>
+        <v>131.35316772</v>
       </c>
       <c r="P45">
-        <v>307.9982082099999</v>
+        <v>306.49072468</v>
       </c>
       <c r="Q45">
-        <v>532.79820821</v>
+        <v>531.29072468</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1109213419719371</v>
+        <v>0.1118559192103403</v>
       </c>
       <c r="T45">
-        <v>1.50395708942118</v>
+        <v>1.525540859361208</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.751460885373343</v>
+        <v>5.620745865251222</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0796717147577906</v>
+        <v>0.07947296459157703</v>
       </c>
       <c r="C46">
-        <v>2865.787849219024</v>
+        <v>2851.751534941217</v>
       </c>
       <c r="D46">
-        <v>4219.779849219024</v>
+        <v>4244.686534941217</v>
       </c>
       <c r="E46">
-        <v>1286.092</v>
+        <v>1325.035</v>
       </c>
       <c r="F46">
-        <v>1713.492</v>
+        <v>1752.435</v>
       </c>
       <c r="G46">
         <v>359.5</v>
@@ -5065,28 +5065,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M46">
-        <v>94.75610760000001</v>
+        <v>96.90965550000001</v>
       </c>
       <c r="N46">
-        <v>437.8438923999999</v>
+        <v>435.6903444999999</v>
       </c>
       <c r="O46">
-        <v>131.35316772</v>
+        <v>130.70710335</v>
       </c>
       <c r="P46">
-        <v>306.49072468</v>
+        <v>304.9832411499999</v>
       </c>
       <c r="Q46">
-        <v>531.29072468</v>
+        <v>529.7832411499999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1118559192103403</v>
+        <v>0.1128244810755946</v>
       </c>
       <c r="T46">
-        <v>1.525540859361208</v>
+        <v>1.547909493662692</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.620745865251222</v>
+        <v>5.495840401578972</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07947296459157703</v>
+        <v>0.07927421442536346</v>
       </c>
       <c r="C47">
-        <v>2851.751534941217</v>
+        <v>2838.010983118906</v>
       </c>
       <c r="D47">
-        <v>4244.686534941217</v>
+        <v>4269.888983118906</v>
       </c>
       <c r="E47">
-        <v>1325.035</v>
+        <v>1363.978</v>
       </c>
       <c r="F47">
-        <v>1752.435</v>
+        <v>1791.378</v>
       </c>
       <c r="G47">
         <v>359.5</v>
@@ -5147,28 +5147,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M47">
-        <v>96.90965550000001</v>
+        <v>99.06320340000001</v>
       </c>
       <c r="N47">
-        <v>435.6903444999999</v>
+        <v>433.5367965999999</v>
       </c>
       <c r="O47">
-        <v>130.70710335</v>
+        <v>130.0610389799999</v>
       </c>
       <c r="P47">
-        <v>304.9832411499999</v>
+        <v>303.47575762</v>
       </c>
       <c r="Q47">
-        <v>529.7832411499999</v>
+        <v>528.2757576199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1128244810755946</v>
+        <v>0.1138289156025249</v>
       </c>
       <c r="T47">
-        <v>1.547909493662692</v>
+        <v>1.571106595901268</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.495840401578972</v>
+        <v>5.376365610240299</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07927421442536346</v>
+        <v>0.07907546425914991</v>
       </c>
       <c r="C48">
-        <v>2838.010983118906</v>
+        <v>2824.571493408021</v>
       </c>
       <c r="D48">
-        <v>4269.888983118906</v>
+        <v>4295.392493408021</v>
       </c>
       <c r="E48">
-        <v>1363.978</v>
+        <v>1402.921</v>
       </c>
       <c r="F48">
-        <v>1791.378</v>
+        <v>1830.321</v>
       </c>
       <c r="G48">
         <v>359.5</v>
@@ -5229,28 +5229,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M48">
-        <v>99.06320340000001</v>
+        <v>101.2167513</v>
       </c>
       <c r="N48">
-        <v>433.5367965999999</v>
+        <v>431.3832486999999</v>
       </c>
       <c r="O48">
-        <v>130.0610389799999</v>
+        <v>129.41497461</v>
       </c>
       <c r="P48">
-        <v>303.47575762</v>
+        <v>301.9682740899999</v>
       </c>
       <c r="Q48">
-        <v>528.2757576199999</v>
+        <v>526.76827409</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1138289156025249</v>
+        <v>0.1148712533191508</v>
       </c>
       <c r="T48">
-        <v>1.571106595901268</v>
+        <v>1.59517906048847</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.376365610240299</v>
+        <v>5.261974852575611</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07907546425914991</v>
+        <v>0.07887671409293634</v>
       </c>
       <c r="C49">
-        <v>2824.571493408021</v>
+        <v>2811.438492842024</v>
       </c>
       <c r="D49">
-        <v>4295.392493408021</v>
+        <v>4321.202492842024</v>
       </c>
       <c r="E49">
-        <v>1402.921</v>
+        <v>1441.864</v>
       </c>
       <c r="F49">
-        <v>1830.321</v>
+        <v>1869.264</v>
       </c>
       <c r="G49">
         <v>359.5</v>
@@ -5311,28 +5311,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M49">
-        <v>101.2167513</v>
+        <v>103.3702992</v>
       </c>
       <c r="N49">
-        <v>431.3832486999999</v>
+        <v>429.2297007999999</v>
       </c>
       <c r="O49">
-        <v>129.41497461</v>
+        <v>128.76891024</v>
       </c>
       <c r="P49">
-        <v>301.9682740899999</v>
+        <v>300.46079056</v>
       </c>
       <c r="Q49">
-        <v>526.76827409</v>
+        <v>525.26079056</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1148712533191508</v>
+        <v>0.1159536809479545</v>
       </c>
       <c r="T49">
-        <v>1.59517906048847</v>
+        <v>1.620177389098256</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.261974852575611</v>
+        <v>5.152350376480287</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07887671409293634</v>
+        <v>0.07867796392672277</v>
       </c>
       <c r="C50">
-        <v>2811.438492842024</v>
+        <v>2798.617539681937</v>
       </c>
       <c r="D50">
-        <v>4321.202492842024</v>
+        <v>4347.324539681937</v>
       </c>
       <c r="E50">
-        <v>1441.864</v>
+        <v>1480.807</v>
       </c>
       <c r="F50">
-        <v>1869.264</v>
+        <v>1908.207</v>
       </c>
       <c r="G50">
         <v>359.5</v>
@@ -5393,28 +5393,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M50">
-        <v>103.3702992</v>
+        <v>105.5238471</v>
       </c>
       <c r="N50">
-        <v>429.2297007999999</v>
+        <v>427.0761528999999</v>
       </c>
       <c r="O50">
-        <v>128.76891024</v>
+        <v>128.12284587</v>
       </c>
       <c r="P50">
-        <v>300.46079056</v>
+        <v>298.9533070299999</v>
       </c>
       <c r="Q50">
-        <v>525.26079056</v>
+        <v>523.7533070299999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1159536809479545</v>
+        <v>0.1170785567190643</v>
       </c>
       <c r="T50">
-        <v>1.620177389098256</v>
+        <v>1.646156044320191</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.152350376480287</v>
+        <v>5.047200368797015</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07867796392672277</v>
+        <v>0.07847921376050922</v>
       </c>
       <c r="C51">
-        <v>2798.617539681937</v>
+        <v>2786.114327406884</v>
       </c>
       <c r="D51">
-        <v>4347.324539681937</v>
+        <v>4373.764327406884</v>
       </c>
       <c r="E51">
-        <v>1480.807</v>
+        <v>1519.75</v>
       </c>
       <c r="F51">
-        <v>1908.207</v>
+        <v>1947.15</v>
       </c>
       <c r="G51">
         <v>359.5</v>
@@ -5475,28 +5475,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M51">
-        <v>105.5238471</v>
+        <v>107.677395</v>
       </c>
       <c r="N51">
-        <v>427.0761528999999</v>
+        <v>424.9226049999999</v>
       </c>
       <c r="O51">
-        <v>128.12284587</v>
+        <v>127.4767815</v>
       </c>
       <c r="P51">
-        <v>298.9533070299999</v>
+        <v>297.4458235</v>
       </c>
       <c r="Q51">
-        <v>523.7533070299999</v>
+        <v>522.2458234999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1170785567190643</v>
+        <v>0.1182484275210184</v>
       </c>
       <c r="T51">
-        <v>1.646156044320191</v>
+        <v>1.673173845751003</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.047200368797015</v>
+        <v>4.946256361421075</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07847921376050922</v>
+        <v>0.07828046359429566</v>
       </c>
       <c r="C52">
-        <v>2786.114327406884</v>
+        <v>2773.934688851137</v>
       </c>
       <c r="D52">
-        <v>4373.764327406884</v>
+        <v>4400.527688851137</v>
       </c>
       <c r="E52">
-        <v>1519.75</v>
+        <v>1558.693</v>
       </c>
       <c r="F52">
-        <v>1947.15</v>
+        <v>1986.093</v>
       </c>
       <c r="G52">
         <v>359.5</v>
@@ -5557,28 +5557,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M52">
-        <v>107.677395</v>
+        <v>109.8309429</v>
       </c>
       <c r="N52">
-        <v>424.9226049999999</v>
+        <v>422.7690570999999</v>
       </c>
       <c r="O52">
-        <v>127.4767815</v>
+        <v>126.83071713</v>
       </c>
       <c r="P52">
-        <v>297.4458235</v>
+        <v>295.9383399699999</v>
       </c>
       <c r="Q52">
-        <v>522.2458234999999</v>
+        <v>520.73833997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1182484275210184</v>
+        <v>0.1194660481516238</v>
       </c>
       <c r="T52">
-        <v>1.673173845751003</v>
+        <v>1.701294414587154</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.946256361421075</v>
+        <v>4.849270942569682</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07828046359429566</v>
+        <v>0.07808171342808209</v>
       </c>
       <c r="C53">
-        <v>2773.934688851137</v>
+        <v>2762.084600493979</v>
       </c>
       <c r="D53">
-        <v>4400.527688851137</v>
+        <v>4427.62060049398</v>
       </c>
       <c r="E53">
-        <v>1558.693</v>
+        <v>1597.636</v>
       </c>
       <c r="F53">
-        <v>1986.093</v>
+        <v>2025.036</v>
       </c>
       <c r="G53">
         <v>359.5</v>
@@ -5639,28 +5639,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M53">
-        <v>109.8309429</v>
+        <v>111.9844908</v>
       </c>
       <c r="N53">
-        <v>422.7690570999999</v>
+        <v>420.6155091999999</v>
       </c>
       <c r="O53">
-        <v>126.83071713</v>
+        <v>126.18465276</v>
       </c>
       <c r="P53">
-        <v>295.9383399699999</v>
+        <v>294.43085644</v>
       </c>
       <c r="Q53">
-        <v>520.73833997</v>
+        <v>519.23085644</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1194660481516238</v>
+        <v>0.120734402975171</v>
       </c>
       <c r="T53">
-        <v>1.701294414587154</v>
+        <v>1.730586673791478</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.849270942569682</v>
+        <v>4.75601573213565</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07808171342808209</v>
+        <v>0.07788296326186853</v>
       </c>
       <c r="C54">
-        <v>2762.084600493979</v>
+        <v>2750.570186909023</v>
       </c>
       <c r="D54">
-        <v>4427.62060049398</v>
+        <v>4455.049186909023</v>
       </c>
       <c r="E54">
-        <v>1597.636</v>
+        <v>1636.579</v>
       </c>
       <c r="F54">
-        <v>2025.036</v>
+        <v>2063.979</v>
       </c>
       <c r="G54">
         <v>359.5</v>
@@ -5721,28 +5721,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M54">
-        <v>111.9844908</v>
+        <v>114.1380387</v>
       </c>
       <c r="N54">
-        <v>420.6155091999999</v>
+        <v>418.4619612999999</v>
       </c>
       <c r="O54">
-        <v>126.18465276</v>
+        <v>125.53858839</v>
       </c>
       <c r="P54">
-        <v>294.43085644</v>
+        <v>292.9233729099999</v>
       </c>
       <c r="Q54">
-        <v>519.23085644</v>
+        <v>517.7233729099999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.120734402975171</v>
+        <v>0.1220567303444011</v>
       </c>
       <c r="T54">
-        <v>1.730586673791478</v>
+        <v>1.76112541211088</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.75601573213565</v>
+        <v>4.666279586246297</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07788296326186853</v>
+        <v>0.07768421309565496</v>
       </c>
       <c r="C55">
-        <v>2750.570186909023</v>
+        <v>2739.397725379939</v>
       </c>
       <c r="D55">
-        <v>4455.049186909023</v>
+        <v>4482.819725379939</v>
       </c>
       <c r="E55">
-        <v>1636.579</v>
+        <v>1675.522</v>
       </c>
       <c r="F55">
-        <v>2063.979</v>
+        <v>2102.922</v>
       </c>
       <c r="G55">
         <v>359.5</v>
@@ -5803,28 +5803,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M55">
-        <v>114.1380387</v>
+        <v>116.2915866</v>
       </c>
       <c r="N55">
-        <v>418.4619612999999</v>
+        <v>416.3084133999999</v>
       </c>
       <c r="O55">
-        <v>125.53858839</v>
+        <v>124.89252402</v>
       </c>
       <c r="P55">
-        <v>292.9233729099999</v>
+        <v>291.41588938</v>
       </c>
       <c r="Q55">
-        <v>517.7233729099999</v>
+        <v>516.2158893799999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1220567303444011</v>
+        <v>0.1234365502079456</v>
       </c>
       <c r="T55">
-        <v>1.76112541211088</v>
+        <v>1.79299192166156</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.666279586246297</v>
+        <v>4.57986700131581</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07768421309565496</v>
+        <v>0.07844796292944139</v>
       </c>
       <c r="C56">
-        <v>2739.397725379939</v>
+        <v>2595.585921542073</v>
       </c>
       <c r="D56">
-        <v>4482.819725379939</v>
+        <v>4377.950921542073</v>
       </c>
       <c r="E56">
-        <v>1675.522</v>
+        <v>1714.465</v>
       </c>
       <c r="F56">
-        <v>2102.922</v>
+        <v>2141.865</v>
       </c>
       <c r="G56">
         <v>359.5</v>
@@ -5885,45 +5885,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M56">
-        <v>116.2915866</v>
+        <v>123.799797</v>
       </c>
       <c r="N56">
-        <v>416.3084133999999</v>
+        <v>408.8002029999999</v>
       </c>
       <c r="O56">
-        <v>124.89252402</v>
+        <v>122.6400609</v>
       </c>
       <c r="P56">
-        <v>291.41588938</v>
+        <v>286.1601420999999</v>
       </c>
       <c r="Q56">
-        <v>516.2158893799999</v>
+        <v>510.9601420999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1234365502079456</v>
+        <v>0.1248776953987587</v>
       </c>
       <c r="T56">
-        <v>1.79299192166156</v>
+        <v>1.826274720525604</v>
       </c>
       <c r="U56">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V56">
         <v>0.3</v>
       </c>
       <c r="W56">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>4.57986700131581</v>
+        <v>4.302107215894706</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07844796292944139</v>
+        <v>0.07826671276322784</v>
       </c>
       <c r="C57">
-        <v>2595.585921542073</v>
+        <v>2581.083472021918</v>
       </c>
       <c r="D57">
-        <v>4377.950921542073</v>
+        <v>4402.391472021918</v>
       </c>
       <c r="E57">
-        <v>1714.465</v>
+        <v>1753.408</v>
       </c>
       <c r="F57">
-        <v>2141.865</v>
+        <v>2180.808</v>
       </c>
       <c r="G57">
         <v>359.5</v>
@@ -5967,28 +5967,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M57">
-        <v>123.799797</v>
+        <v>126.0507024</v>
       </c>
       <c r="N57">
-        <v>408.8002029999999</v>
+        <v>406.5492975999999</v>
       </c>
       <c r="O57">
-        <v>122.6400609</v>
+        <v>121.96478928</v>
       </c>
       <c r="P57">
-        <v>286.1601420999999</v>
+        <v>284.5845083199999</v>
       </c>
       <c r="Q57">
-        <v>510.9601420999999</v>
+        <v>509.38450832</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1248776953987587</v>
+        <v>0.1263843471891542</v>
       </c>
       <c r="T57">
-        <v>1.826274720525604</v>
+        <v>1.861070373883469</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.302107215894706</v>
+        <v>4.225283872753729</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07826671276322784</v>
+        <v>0.07808546259701428</v>
       </c>
       <c r="C58">
-        <v>2581.083472021918</v>
+        <v>2566.855440365439</v>
       </c>
       <c r="D58">
-        <v>4402.391472021918</v>
+        <v>4427.106440365439</v>
       </c>
       <c r="E58">
-        <v>1753.408</v>
+        <v>1792.351</v>
       </c>
       <c r="F58">
-        <v>2180.808</v>
+        <v>2219.751</v>
       </c>
       <c r="G58">
         <v>359.5</v>
@@ -6049,28 +6049,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M58">
-        <v>126.0507024</v>
+        <v>128.3016078</v>
       </c>
       <c r="N58">
-        <v>406.5492975999999</v>
+        <v>404.2983921999999</v>
       </c>
       <c r="O58">
-        <v>121.96478928</v>
+        <v>121.2895176599999</v>
       </c>
       <c r="P58">
-        <v>284.5845083199999</v>
+        <v>283.0088745399999</v>
       </c>
       <c r="Q58">
-        <v>509.38450832</v>
+        <v>507.8088745399999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1263843471891542</v>
+        <v>0.12796107580701</v>
       </c>
       <c r="T58">
-        <v>1.861070373883469</v>
+        <v>1.897484429723094</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.225283872753729</v>
+        <v>4.151156085512436</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07808546259701428</v>
+        <v>0.07790421243080073</v>
       </c>
       <c r="C59">
-        <v>2566.855440365439</v>
+        <v>2552.906474400408</v>
       </c>
       <c r="D59">
-        <v>4427.106440365439</v>
+        <v>4452.100474400409</v>
       </c>
       <c r="E59">
-        <v>1792.351</v>
+        <v>1831.294</v>
       </c>
       <c r="F59">
-        <v>2219.751</v>
+        <v>2258.694</v>
       </c>
       <c r="G59">
         <v>359.5</v>
@@ -6131,28 +6131,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M59">
-        <v>128.3016078</v>
+        <v>130.5525132</v>
       </c>
       <c r="N59">
-        <v>404.2983921999999</v>
+        <v>402.0474867999999</v>
       </c>
       <c r="O59">
-        <v>121.2895176599999</v>
+        <v>120.61424604</v>
       </c>
       <c r="P59">
-        <v>283.0088745399999</v>
+        <v>281.4332407599999</v>
       </c>
       <c r="Q59">
-        <v>507.8088745399999</v>
+        <v>506.2332407599999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.12796107580701</v>
+        <v>0.1296128867400017</v>
       </c>
       <c r="T59">
-        <v>1.897484429723094</v>
+        <v>1.935632488221749</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.151156085512436</v>
+        <v>4.07958442886567</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07790421243080073</v>
+        <v>0.07772296226458716</v>
       </c>
       <c r="C60">
-        <v>2552.906474400409</v>
+        <v>2539.241327511168</v>
       </c>
       <c r="D60">
-        <v>4452.100474400409</v>
+        <v>4477.378327511168</v>
       </c>
       <c r="E60">
-        <v>1831.294</v>
+        <v>1870.237</v>
       </c>
       <c r="F60">
-        <v>2258.694</v>
+        <v>2297.637</v>
       </c>
       <c r="G60">
         <v>359.5</v>
@@ -6213,28 +6213,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M60">
-        <v>130.5525132</v>
+        <v>132.8034186</v>
       </c>
       <c r="N60">
-        <v>402.0474867999999</v>
+        <v>399.7965813999999</v>
       </c>
       <c r="O60">
-        <v>120.61424604</v>
+        <v>119.93897442</v>
       </c>
       <c r="P60">
-        <v>281.4332407599999</v>
+        <v>279.85760698</v>
       </c>
       <c r="Q60">
-        <v>506.2332407599999</v>
+        <v>504.65760698</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1296128867400017</v>
+        <v>0.1313452738160662</v>
       </c>
       <c r="T60">
-        <v>1.935632488221748</v>
+        <v>1.975641427622776</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.07958442886567</v>
+        <v>4.010438930071337</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07772296226458716</v>
+        <v>0.07901171209837358</v>
       </c>
       <c r="C61">
-        <v>2539.241327511168</v>
+        <v>2326.557794102729</v>
       </c>
       <c r="D61">
-        <v>4477.378327511168</v>
+        <v>4303.637794102729</v>
       </c>
       <c r="E61">
-        <v>1870.237</v>
+        <v>1909.18</v>
       </c>
       <c r="F61">
-        <v>2297.637</v>
+        <v>2336.58</v>
       </c>
       <c r="G61">
         <v>359.5</v>
@@ -6295,45 +6295,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M61">
-        <v>132.8034186</v>
+        <v>143.232354</v>
       </c>
       <c r="N61">
-        <v>399.7965813999999</v>
+        <v>389.3676459999999</v>
       </c>
       <c r="O61">
-        <v>119.93897442</v>
+        <v>116.8102938</v>
       </c>
       <c r="P61">
-        <v>279.85760698</v>
+        <v>272.5573522</v>
       </c>
       <c r="Q61">
-        <v>504.65760698</v>
+        <v>497.3573522</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1313452738160662</v>
+        <v>0.133164280245934</v>
       </c>
       <c r="T61">
-        <v>1.975641427622776</v>
+        <v>2.017650813993856</v>
       </c>
       <c r="U61">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V61">
         <v>0.3</v>
       </c>
       <c r="W61">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.010438930071337</v>
+        <v>3.718433615913343</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07901171209837358</v>
+        <v>0.07885496193216003</v>
       </c>
       <c r="C62">
-        <v>2326.557794102729</v>
+        <v>2308.02310499212</v>
       </c>
       <c r="D62">
-        <v>4303.637794102729</v>
+        <v>4324.04610499212</v>
       </c>
       <c r="E62">
-        <v>1909.18</v>
+        <v>1948.123</v>
       </c>
       <c r="F62">
-        <v>2336.58</v>
+        <v>2375.523</v>
       </c>
       <c r="G62">
         <v>359.5</v>
@@ -6377,28 +6377,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M62">
-        <v>143.232354</v>
+        <v>145.6195599</v>
       </c>
       <c r="N62">
-        <v>389.3676459999999</v>
+        <v>386.9804400999999</v>
       </c>
       <c r="O62">
-        <v>116.8102938</v>
+        <v>116.09413203</v>
       </c>
       <c r="P62">
-        <v>272.5573522</v>
+        <v>270.8863080699999</v>
       </c>
       <c r="Q62">
-        <v>497.3573522</v>
+        <v>495.6863080699999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.133164280245934</v>
+        <v>0.1350765690568206</v>
       </c>
       <c r="T62">
-        <v>2.017650813993856</v>
+        <v>2.061814527871145</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.718433615913343</v>
+        <v>3.657475687783615</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07885496193216003</v>
+        <v>0.07869821176594646</v>
       </c>
       <c r="C63">
-        <v>2308.02310499212</v>
+        <v>2289.682894909542</v>
       </c>
       <c r="D63">
-        <v>4324.04610499212</v>
+        <v>4344.648894909542</v>
       </c>
       <c r="E63">
-        <v>1948.123</v>
+        <v>1987.066</v>
       </c>
       <c r="F63">
-        <v>2375.523</v>
+        <v>2414.466</v>
       </c>
       <c r="G63">
         <v>359.5</v>
@@ -6459,28 +6459,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M63">
-        <v>145.6195599</v>
+        <v>148.0067658</v>
       </c>
       <c r="N63">
-        <v>386.9804400999999</v>
+        <v>384.5932341999999</v>
       </c>
       <c r="O63">
-        <v>116.09413203</v>
+        <v>115.37797026</v>
       </c>
       <c r="P63">
-        <v>270.8863080699999</v>
+        <v>269.2152639399999</v>
       </c>
       <c r="Q63">
-        <v>495.6863080699999</v>
+        <v>494.01526394</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1350765690568206</v>
+        <v>0.1370895046472276</v>
       </c>
       <c r="T63">
-        <v>2.061814527871145</v>
+        <v>2.108302647741975</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.657475687783615</v>
+        <v>3.598484144432267</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07869821176594646</v>
+        <v>0.07854146159973291</v>
       </c>
       <c r="C64">
-        <v>2289.682894909542</v>
+        <v>2271.539957067493</v>
       </c>
       <c r="D64">
-        <v>4344.648894909542</v>
+        <v>4365.448957067493</v>
       </c>
       <c r="E64">
-        <v>1987.066</v>
+        <v>2026.009</v>
       </c>
       <c r="F64">
-        <v>2414.466</v>
+        <v>2453.409</v>
       </c>
       <c r="G64">
         <v>359.5</v>
@@ -6541,28 +6541,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M64">
-        <v>148.0067658</v>
+        <v>150.3939717</v>
       </c>
       <c r="N64">
-        <v>384.5932341999999</v>
+        <v>382.2060282999999</v>
       </c>
       <c r="O64">
-        <v>115.37797026</v>
+        <v>114.66180849</v>
       </c>
       <c r="P64">
-        <v>269.2152639399999</v>
+        <v>267.54421981</v>
       </c>
       <c r="Q64">
-        <v>494.01526394</v>
+        <v>492.34421981</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1370895046472276</v>
+        <v>0.1392112475668457</v>
       </c>
       <c r="T64">
-        <v>2.108302647741975</v>
+        <v>2.157303638957175</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.598484144432267</v>
+        <v>3.541365348488898</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07854146159973291</v>
+        <v>0.07963911143351934</v>
       </c>
       <c r="C65">
-        <v>2271.539957067493</v>
+        <v>2090.993524851426</v>
       </c>
       <c r="D65">
-        <v>4365.448957067493</v>
+        <v>4223.845524851426</v>
       </c>
       <c r="E65">
-        <v>2026.009</v>
+        <v>2064.952</v>
       </c>
       <c r="F65">
-        <v>2453.409</v>
+        <v>2492.352</v>
       </c>
       <c r="G65">
         <v>359.5</v>
@@ -6623,45 +6623,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M65">
-        <v>150.3939717</v>
+        <v>159.7597632</v>
       </c>
       <c r="N65">
-        <v>382.2060282999999</v>
+        <v>372.8402367999998</v>
       </c>
       <c r="O65">
-        <v>114.66180849</v>
+        <v>111.85207104</v>
       </c>
       <c r="P65">
-        <v>267.54421981</v>
+        <v>260.9881657599999</v>
       </c>
       <c r="Q65">
-        <v>492.34421981</v>
+        <v>485.7881657599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1392112475668457</v>
+        <v>0.1414508650931093</v>
       </c>
       <c r="T65">
-        <v>2.157303638957175</v>
+        <v>2.209026907462108</v>
       </c>
       <c r="U65">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V65">
         <v>0.3</v>
       </c>
       <c r="W65">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y65">
-        <v>3.541365348488898</v>
+        <v>3.333755567309202</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07963911143351934</v>
+        <v>0.07950196126730578</v>
       </c>
       <c r="C66">
-        <v>2090.993524851426</v>
+        <v>2069.239468580816</v>
       </c>
       <c r="D66">
-        <v>4223.845524851426</v>
+        <v>4241.034468580816</v>
       </c>
       <c r="E66">
-        <v>2064.952</v>
+        <v>2103.895</v>
       </c>
       <c r="F66">
-        <v>2492.352</v>
+        <v>2531.295</v>
       </c>
       <c r="G66">
         <v>359.5</v>
@@ -6705,28 +6705,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M66">
-        <v>159.7597632</v>
+        <v>162.2560095</v>
       </c>
       <c r="N66">
-        <v>372.8402367999998</v>
+        <v>370.3439904999999</v>
       </c>
       <c r="O66">
-        <v>111.85207104</v>
+        <v>111.10319715</v>
       </c>
       <c r="P66">
-        <v>260.9881657599999</v>
+        <v>259.2407933499999</v>
       </c>
       <c r="Q66">
-        <v>485.7881657599999</v>
+        <v>484.0407933499999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1414508650931093</v>
+        <v>0.1438184607637308</v>
       </c>
       <c r="T66">
-        <v>2.209026907462108</v>
+        <v>2.26370579131018</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.333755567309202</v>
+        <v>3.28246702011983</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07950196126730578</v>
+        <v>0.07936481110109223</v>
       </c>
       <c r="C67">
-        <v>2069.239468580816</v>
+        <v>2047.625884811742</v>
       </c>
       <c r="D67">
-        <v>4241.034468580816</v>
+        <v>4258.363884811743</v>
       </c>
       <c r="E67">
-        <v>2103.895</v>
+        <v>2142.838</v>
       </c>
       <c r="F67">
-        <v>2531.295</v>
+        <v>2570.238</v>
       </c>
       <c r="G67">
         <v>359.5</v>
@@ -6787,28 +6787,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M67">
-        <v>162.2560095</v>
+        <v>164.7522558</v>
       </c>
       <c r="N67">
-        <v>370.3439904999999</v>
+        <v>367.8477441999999</v>
       </c>
       <c r="O67">
-        <v>111.10319715</v>
+        <v>110.35432326</v>
       </c>
       <c r="P67">
-        <v>259.2407933499999</v>
+        <v>257.4934209399999</v>
       </c>
       <c r="Q67">
-        <v>484.0407933499999</v>
+        <v>482.2934209399999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1438184607637308</v>
+        <v>0.1463253267679183</v>
       </c>
       <c r="T67">
-        <v>2.26370579131018</v>
+        <v>2.321601080090492</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.28246702011983</v>
+        <v>3.232732671330135</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07936481110109223</v>
+        <v>0.07922766093487867</v>
       </c>
       <c r="C68">
-        <v>2047.625884811742</v>
+        <v>2026.154502575771</v>
       </c>
       <c r="D68">
-        <v>4258.363884811743</v>
+        <v>4275.835502575772</v>
       </c>
       <c r="E68">
-        <v>2142.838</v>
+        <v>2181.781</v>
       </c>
       <c r="F68">
-        <v>2570.238</v>
+        <v>2609.181</v>
       </c>
       <c r="G68">
         <v>359.5</v>
@@ -6869,28 +6869,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M68">
-        <v>164.7522558</v>
+        <v>167.2485021000001</v>
       </c>
       <c r="N68">
-        <v>367.8477441999999</v>
+        <v>365.3514978999999</v>
       </c>
       <c r="O68">
-        <v>110.35432326</v>
+        <v>109.60544937</v>
       </c>
       <c r="P68">
-        <v>257.4934209399999</v>
+        <v>255.7460485299999</v>
       </c>
       <c r="Q68">
-        <v>482.2934209399999</v>
+        <v>480.5460485299999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1463253267679183</v>
+        <v>0.1489841240450869</v>
       </c>
       <c r="T68">
-        <v>2.321601080090492</v>
+        <v>2.383005174251429</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.232732671330135</v>
+        <v>3.184482929966999</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07922766093487867</v>
+        <v>0.07909051076866509</v>
       </c>
       <c r="C69">
-        <v>2026.154502575771</v>
+        <v>2004.827079397505</v>
       </c>
       <c r="D69">
-        <v>4275.835502575772</v>
+        <v>4293.451079397505</v>
       </c>
       <c r="E69">
-        <v>2181.781</v>
+        <v>2220.724</v>
       </c>
       <c r="F69">
-        <v>2609.181</v>
+        <v>2648.124</v>
       </c>
       <c r="G69">
         <v>359.5</v>
@@ -6951,28 +6951,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M69">
-        <v>167.2485021000001</v>
+        <v>169.7447484</v>
       </c>
       <c r="N69">
-        <v>365.3514978999999</v>
+        <v>362.8552515999999</v>
       </c>
       <c r="O69">
-        <v>109.60544937</v>
+        <v>108.85657548</v>
       </c>
       <c r="P69">
-        <v>255.7460485299999</v>
+        <v>253.9986761199999</v>
       </c>
       <c r="Q69">
-        <v>480.5460485299999</v>
+        <v>478.7986761199999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1489841240450869</v>
+        <v>0.1518090961520784</v>
       </c>
       <c r="T69">
-        <v>2.383005174251429</v>
+        <v>2.448247024297423</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.184482929966999</v>
+        <v>3.137652298643955</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07909051076866509</v>
+        <v>0.07895336060245155</v>
       </c>
       <c r="C70">
-        <v>2004.827079397505</v>
+        <v>1983.645401883936</v>
       </c>
       <c r="D70">
-        <v>4293.451079397505</v>
+        <v>4311.212401883937</v>
       </c>
       <c r="E70">
-        <v>2220.724</v>
+        <v>2259.667</v>
       </c>
       <c r="F70">
-        <v>2648.124</v>
+        <v>2687.067</v>
       </c>
       <c r="G70">
         <v>359.5</v>
@@ -7033,28 +7033,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M70">
-        <v>169.7447484</v>
+        <v>172.2409947</v>
       </c>
       <c r="N70">
-        <v>362.8552515999999</v>
+        <v>360.3590052999999</v>
       </c>
       <c r="O70">
-        <v>108.85657548</v>
+        <v>108.10770159</v>
       </c>
       <c r="P70">
-        <v>253.9986761199999</v>
+        <v>252.2513037099999</v>
       </c>
       <c r="Q70">
-        <v>478.7986761199999</v>
+        <v>477.0513037099999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1518090961520784</v>
+        <v>0.1548163245240373</v>
       </c>
       <c r="T70">
-        <v>2.448247024297423</v>
+        <v>2.51769802595929</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.137652298643955</v>
+        <v>3.092179076924477</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07895336060245155</v>
+        <v>0.07881621043623797</v>
       </c>
       <c r="C71">
-        <v>1983.645401883936</v>
+        <v>1962.611286328513</v>
       </c>
       <c r="D71">
-        <v>4311.212401883937</v>
+        <v>4329.121286328513</v>
       </c>
       <c r="E71">
-        <v>2259.667</v>
+        <v>2298.61</v>
       </c>
       <c r="F71">
-        <v>2687.067</v>
+        <v>2726.01</v>
       </c>
       <c r="G71">
         <v>359.5</v>
@@ -7115,28 +7115,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M71">
-        <v>172.2409947</v>
+        <v>174.737241</v>
       </c>
       <c r="N71">
-        <v>360.3590052999999</v>
+        <v>357.8627589999999</v>
       </c>
       <c r="O71">
-        <v>108.10770159</v>
+        <v>107.3588277</v>
       </c>
       <c r="P71">
-        <v>252.2513037099999</v>
+        <v>250.5039312999999</v>
       </c>
       <c r="Q71">
-        <v>477.0513037099999</v>
+        <v>475.3039312999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1548163245240373</v>
+        <v>0.1580240347874599</v>
       </c>
       <c r="T71">
-        <v>2.51769802595929</v>
+        <v>2.591779094398613</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.092179076924477</v>
+        <v>3.048005090111271</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07881621043623797</v>
+        <v>0.07867906027002441</v>
       </c>
       <c r="C72">
-        <v>1962.611286328513</v>
+        <v>1941.726579330272</v>
       </c>
       <c r="D72">
-        <v>4329.121286328513</v>
+        <v>4347.179579330273</v>
       </c>
       <c r="E72">
-        <v>2298.61</v>
+        <v>2337.553</v>
       </c>
       <c r="F72">
-        <v>2726.01</v>
+        <v>2764.953</v>
       </c>
       <c r="G72">
         <v>359.5</v>
@@ -7197,28 +7197,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M72">
-        <v>174.737241</v>
+        <v>177.2334873</v>
       </c>
       <c r="N72">
-        <v>357.8627589999999</v>
+        <v>355.3665126999999</v>
       </c>
       <c r="O72">
-        <v>107.3588277</v>
+        <v>106.60995381</v>
       </c>
       <c r="P72">
-        <v>250.5039312999999</v>
+        <v>248.7565588899999</v>
       </c>
       <c r="Q72">
-        <v>475.3039312999999</v>
+        <v>473.5565588899999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1580240347874599</v>
+        <v>0.1614529664483601</v>
       </c>
       <c r="T72">
-        <v>2.591779094398613</v>
+        <v>2.670969202040648</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.048005090111271</v>
+        <v>3.005075440954774</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07867906027002441</v>
+        <v>0.08247311010381086</v>
       </c>
       <c r="C73">
-        <v>1941.726579330273</v>
+        <v>1453.042177150043</v>
       </c>
       <c r="D73">
-        <v>4347.179579330273</v>
+        <v>3897.438177150043</v>
       </c>
       <c r="E73">
-        <v>2337.553</v>
+        <v>2376.496</v>
       </c>
       <c r="F73">
-        <v>2764.953</v>
+        <v>2803.896</v>
       </c>
       <c r="G73">
         <v>359.5</v>
@@ -7279,45 +7279,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M73">
-        <v>177.2334873</v>
+        <v>201.6001224</v>
       </c>
       <c r="N73">
-        <v>355.3665126999999</v>
+        <v>330.9998775999999</v>
       </c>
       <c r="O73">
-        <v>106.60995381</v>
+        <v>99.29996327999996</v>
       </c>
       <c r="P73">
-        <v>248.75655889</v>
+        <v>231.6999143199999</v>
       </c>
       <c r="Q73">
-        <v>473.55655889</v>
+        <v>456.4999143199999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.16145296644836</v>
+        <v>0.1651268217993245</v>
       </c>
       <c r="T73">
-        <v>2.670969202040647</v>
+        <v>2.755815745942828</v>
       </c>
       <c r="U73">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V73">
         <v>0.3</v>
       </c>
       <c r="W73">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.005075440954775</v>
+        <v>2.64186347537654</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08247311010381086</v>
+        <v>0.08239055993759729</v>
       </c>
       <c r="C74">
-        <v>1453.042177150043</v>
+        <v>1422.891996114266</v>
       </c>
       <c r="D74">
-        <v>3897.438177150043</v>
+        <v>3906.230996114266</v>
       </c>
       <c r="E74">
-        <v>2376.496</v>
+        <v>2415.439</v>
       </c>
       <c r="F74">
-        <v>2803.896</v>
+        <v>2842.839</v>
       </c>
       <c r="G74">
         <v>359.5</v>
@@ -7361,28 +7361,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M74">
-        <v>201.6001224</v>
+        <v>204.4001241</v>
       </c>
       <c r="N74">
-        <v>330.9998775999999</v>
+        <v>328.1998758999999</v>
       </c>
       <c r="O74">
-        <v>99.29996327999996</v>
+        <v>98.45996276999998</v>
       </c>
       <c r="P74">
-        <v>231.6999143199999</v>
+        <v>229.73991313</v>
       </c>
       <c r="Q74">
-        <v>456.4999143199999</v>
+        <v>454.5399131299999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1651268217993245</v>
+        <v>0.1690728145836937</v>
       </c>
       <c r="T74">
-        <v>2.755815745942828</v>
+        <v>2.846947219022948</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.64186347537654</v>
+        <v>2.605673564754944</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08239055993759729</v>
+        <v>0.08230800977138372</v>
       </c>
       <c r="C75">
-        <v>1422.891996114266</v>
+        <v>1392.781578882187</v>
       </c>
       <c r="D75">
-        <v>3906.230996114266</v>
+        <v>3915.063578882187</v>
       </c>
       <c r="E75">
-        <v>2415.439</v>
+        <v>2454.382</v>
       </c>
       <c r="F75">
-        <v>2842.839</v>
+        <v>2881.782</v>
       </c>
       <c r="G75">
         <v>359.5</v>
@@ -7443,28 +7443,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M75">
-        <v>204.4001241</v>
+        <v>207.2001258</v>
       </c>
       <c r="N75">
-        <v>328.1998758999999</v>
+        <v>325.3998741999999</v>
       </c>
       <c r="O75">
-        <v>98.45996276999998</v>
+        <v>97.61996225999997</v>
       </c>
       <c r="P75">
-        <v>229.73991313</v>
+        <v>227.7799119399999</v>
       </c>
       <c r="Q75">
-        <v>454.5399131299999</v>
+        <v>452.5799119399999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1690728145836937</v>
+        <v>0.1733223452745528</v>
       </c>
       <c r="T75">
-        <v>2.846947219022948</v>
+        <v>2.945088805416923</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.605673564754944</v>
+        <v>2.570461759825823</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08230800977138372</v>
+        <v>0.08222545960517016</v>
       </c>
       <c r="C76">
-        <v>1392.781578882187</v>
+        <v>1362.711195801136</v>
       </c>
       <c r="D76">
-        <v>3915.063578882187</v>
+        <v>3923.936195801137</v>
       </c>
       <c r="E76">
-        <v>2454.382</v>
+        <v>2493.325</v>
       </c>
       <c r="F76">
-        <v>2881.782</v>
+        <v>2920.725</v>
       </c>
       <c r="G76">
         <v>359.5</v>
@@ -7525,28 +7525,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M76">
-        <v>207.2001258</v>
+        <v>210.0001275</v>
       </c>
       <c r="N76">
-        <v>325.3998741999999</v>
+        <v>322.5998724999998</v>
       </c>
       <c r="O76">
-        <v>97.61996225999997</v>
+        <v>96.77996174999994</v>
       </c>
       <c r="P76">
-        <v>227.7799119399999</v>
+        <v>225.8199107499999</v>
       </c>
       <c r="Q76">
-        <v>452.5799119399999</v>
+        <v>450.6199107499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1733223452745528</v>
+        <v>0.1779118384206807</v>
       </c>
       <c r="T76">
-        <v>2.945088805416923</v>
+        <v>3.051081718722417</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.570461759825823</v>
+        <v>2.536188936361478</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08222545960517016</v>
+        <v>0.08214290943895661</v>
       </c>
       <c r="C77">
-        <v>1362.711195801136</v>
+        <v>1332.681119674744</v>
       </c>
       <c r="D77">
-        <v>3923.936195801137</v>
+        <v>3932.849119674743</v>
       </c>
       <c r="E77">
-        <v>2493.325</v>
+        <v>2532.268</v>
       </c>
       <c r="F77">
-        <v>2920.725</v>
+        <v>2959.668</v>
       </c>
       <c r="G77">
         <v>359.5</v>
@@ -7607,28 +7607,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M77">
-        <v>210.0001275</v>
+        <v>212.8001292</v>
       </c>
       <c r="N77">
-        <v>322.5998724999998</v>
+        <v>319.7998707999999</v>
       </c>
       <c r="O77">
-        <v>96.77996174999994</v>
+        <v>95.93996123999996</v>
       </c>
       <c r="P77">
-        <v>225.8199107499999</v>
+        <v>223.8599095599999</v>
       </c>
       <c r="Q77">
-        <v>450.6199107499999</v>
+        <v>448.65990956</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1779118384206807</v>
+        <v>0.1828837893289859</v>
       </c>
       <c r="T77">
-        <v>3.051081718722417</v>
+        <v>3.165907374803368</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.536188936361478</v>
+        <v>2.502818029304091</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08214290943895661</v>
+        <v>0.08416245927274305</v>
       </c>
       <c r="C78">
-        <v>1332.681119674744</v>
+        <v>1086.697566578879</v>
       </c>
       <c r="D78">
-        <v>3932.849119674743</v>
+        <v>3725.808566578879</v>
       </c>
       <c r="E78">
-        <v>2532.268</v>
+        <v>2571.211</v>
       </c>
       <c r="F78">
-        <v>2959.668</v>
+        <v>2998.611</v>
       </c>
       <c r="G78">
         <v>359.5</v>
@@ -7689,45 +7689,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M78">
-        <v>212.8001292</v>
+        <v>227.2947138</v>
       </c>
       <c r="N78">
-        <v>319.7998707999999</v>
+        <v>305.3052861999998</v>
       </c>
       <c r="O78">
-        <v>95.93996123999996</v>
+        <v>91.59158585999995</v>
       </c>
       <c r="P78">
-        <v>223.8599095599999</v>
+        <v>213.7137003399999</v>
       </c>
       <c r="Q78">
-        <v>448.65990956</v>
+        <v>438.5137003399999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1828837893289859</v>
+        <v>0.188288083794535</v>
       </c>
       <c r="T78">
-        <v>3.165907374803368</v>
+        <v>3.290717870543532</v>
       </c>
       <c r="U78">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.502818029304091</v>
+        <v>2.343213315856709</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08416245927274305</v>
+        <v>0.08410720910652948</v>
       </c>
       <c r="C79">
-        <v>1086.697566578879</v>
+        <v>1053.128269006821</v>
       </c>
       <c r="D79">
-        <v>3725.808566578879</v>
+        <v>3731.182269006821</v>
       </c>
       <c r="E79">
-        <v>2571.211</v>
+        <v>2610.154</v>
       </c>
       <c r="F79">
-        <v>2998.611</v>
+        <v>3037.554</v>
       </c>
       <c r="G79">
         <v>359.5</v>
@@ -7771,28 +7771,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M79">
-        <v>227.2947138</v>
+        <v>230.2465932</v>
       </c>
       <c r="N79">
-        <v>305.3052861999998</v>
+        <v>302.3534067999999</v>
       </c>
       <c r="O79">
-        <v>91.59158585999995</v>
+        <v>90.70602203999997</v>
       </c>
       <c r="P79">
-        <v>213.7137003399999</v>
+        <v>211.6473847599999</v>
       </c>
       <c r="Q79">
-        <v>438.5137003399999</v>
+        <v>436.44738476</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.188288083794535</v>
+        <v>0.1941836777569522</v>
       </c>
       <c r="T79">
-        <v>3.290717870543532</v>
+        <v>3.426874774987348</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.343213315856709</v>
+        <v>2.313172119499573</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08410720910652948</v>
+        <v>0.08405195894031592</v>
       </c>
       <c r="C80">
-        <v>1053.128269006821</v>
+        <v>1019.574494715688</v>
       </c>
       <c r="D80">
-        <v>3731.182269006821</v>
+        <v>3736.571494715689</v>
       </c>
       <c r="E80">
-        <v>2610.154</v>
+        <v>2649.097</v>
       </c>
       <c r="F80">
-        <v>3037.554</v>
+        <v>3076.497</v>
       </c>
       <c r="G80">
         <v>359.5</v>
@@ -7853,28 +7853,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M80">
-        <v>230.2465932</v>
+        <v>233.1984726</v>
       </c>
       <c r="N80">
-        <v>302.3534067999999</v>
+        <v>299.4015273999998</v>
       </c>
       <c r="O80">
-        <v>90.70602203999997</v>
+        <v>89.82045821999995</v>
       </c>
       <c r="P80">
-        <v>211.6473847599999</v>
+        <v>209.5810691799999</v>
       </c>
       <c r="Q80">
-        <v>436.44738476</v>
+        <v>434.3810691799999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1941836777569522</v>
+        <v>0.2006407568586473</v>
       </c>
       <c r="T80">
-        <v>3.426874774987348</v>
+        <v>3.575999003663909</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.313172119499573</v>
+        <v>2.283891459759071</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08405195894031592</v>
+        <v>0.08399670877410235</v>
       </c>
       <c r="C81">
-        <v>1019.574494715688</v>
+        <v>986.0363110670878</v>
       </c>
       <c r="D81">
-        <v>3736.571494715689</v>
+        <v>3741.976311067088</v>
       </c>
       <c r="E81">
-        <v>2649.097</v>
+        <v>2688.04</v>
       </c>
       <c r="F81">
-        <v>3076.497</v>
+        <v>3115.440000000001</v>
       </c>
       <c r="G81">
         <v>359.5</v>
@@ -7935,28 +7935,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M81">
-        <v>233.1984726</v>
+        <v>236.1503520000001</v>
       </c>
       <c r="N81">
-        <v>299.4015273999998</v>
+        <v>296.4496479999999</v>
       </c>
       <c r="O81">
-        <v>89.82045821999995</v>
+        <v>88.93489439999995</v>
       </c>
       <c r="P81">
-        <v>209.5810691799999</v>
+        <v>207.5147535999999</v>
       </c>
       <c r="Q81">
-        <v>434.3810691799999</v>
+        <v>432.3147535999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2006407568586473</v>
+        <v>0.2077435438705118</v>
       </c>
       <c r="T81">
-        <v>3.575999003663909</v>
+        <v>3.740035655208124</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.283891459759071</v>
+        <v>2.255342816512083</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08399670877410235</v>
+        <v>0.08394145860788879</v>
       </c>
       <c r="C82">
-        <v>986.0363110670878</v>
+        <v>952.5137858129306</v>
       </c>
       <c r="D82">
-        <v>3741.976311067088</v>
+        <v>3747.396785812931</v>
       </c>
       <c r="E82">
-        <v>2688.04</v>
+        <v>2726.983</v>
       </c>
       <c r="F82">
-        <v>3115.440000000001</v>
+        <v>3154.383</v>
       </c>
       <c r="G82">
         <v>359.5</v>
@@ -8017,28 +8017,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M82">
-        <v>236.1503520000001</v>
+        <v>239.1022314000001</v>
       </c>
       <c r="N82">
-        <v>296.4496479999999</v>
+        <v>293.4977685999999</v>
       </c>
       <c r="O82">
-        <v>88.93489439999995</v>
+        <v>88.04933057999996</v>
       </c>
       <c r="P82">
-        <v>207.5147535999999</v>
+        <v>205.4484380199999</v>
       </c>
       <c r="Q82">
-        <v>432.3147535999999</v>
+        <v>430.2484380199999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2077435438705118</v>
+        <v>0.2155939926730989</v>
       </c>
       <c r="T82">
-        <v>3.740035655208124</v>
+        <v>3.921339322704363</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.255342816512083</v>
+        <v>2.227499078036625</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08394145860788879</v>
+        <v>0.08388620844167524</v>
       </c>
       <c r="C83">
-        <v>952.5137858129306</v>
+        <v>919.0069870982684</v>
       </c>
       <c r="D83">
-        <v>3747.396785812931</v>
+        <v>3752.832987098269</v>
       </c>
       <c r="E83">
-        <v>2726.983</v>
+        <v>2765.926</v>
       </c>
       <c r="F83">
-        <v>3154.383</v>
+        <v>3193.326</v>
       </c>
       <c r="G83">
         <v>359.5</v>
@@ -8099,28 +8099,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M83">
-        <v>239.1022314000001</v>
+        <v>242.0541108</v>
       </c>
       <c r="N83">
-        <v>293.4977685999999</v>
+        <v>290.5458891999999</v>
       </c>
       <c r="O83">
-        <v>88.04933057999996</v>
+        <v>87.16376675999996</v>
       </c>
       <c r="P83">
-        <v>205.4484380199999</v>
+        <v>203.3821224399999</v>
       </c>
       <c r="Q83">
-        <v>430.2484380199999</v>
+        <v>428.1821224399999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2155939926730989</v>
+        <v>0.2243167135648625</v>
       </c>
       <c r="T83">
-        <v>3.921339322704363</v>
+        <v>4.122787842144629</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.227499078036625</v>
+        <v>2.200334455133739</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08388620844167524</v>
+        <v>0.08383095827546166</v>
       </c>
       <c r="C84">
-        <v>919.0069870982684</v>
+        <v>885.5159834641545</v>
       </c>
       <c r="D84">
-        <v>3752.832987098269</v>
+        <v>3758.284983464155</v>
       </c>
       <c r="E84">
-        <v>2765.926</v>
+        <v>2804.869</v>
       </c>
       <c r="F84">
-        <v>3193.326</v>
+        <v>3232.269</v>
       </c>
       <c r="G84">
         <v>359.5</v>
@@ -8181,28 +8181,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M84">
-        <v>242.0541108</v>
+        <v>245.0059902</v>
       </c>
       <c r="N84">
-        <v>290.5458891999999</v>
+        <v>287.5940097999999</v>
       </c>
       <c r="O84">
-        <v>87.16376675999996</v>
+        <v>86.27820293999996</v>
       </c>
       <c r="P84">
-        <v>203.3821224399999</v>
+        <v>201.3158068599999</v>
       </c>
       <c r="Q84">
-        <v>428.1821224399999</v>
+        <v>426.1158068599999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2243167135648625</v>
+        <v>0.2340656369144805</v>
       </c>
       <c r="T84">
-        <v>4.122787842144629</v>
+        <v>4.347936187401396</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.200334455133739</v>
+        <v>2.17382440145743</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08383095827546166</v>
+        <v>0.08377570810924811</v>
       </c>
       <c r="C85">
-        <v>885.5159834641545</v>
+        <v>852.0408438505083</v>
       </c>
       <c r="D85">
-        <v>3758.284983464155</v>
+        <v>3763.752843850508</v>
       </c>
       <c r="E85">
-        <v>2804.869</v>
+        <v>2843.812</v>
       </c>
       <c r="F85">
-        <v>3232.269</v>
+        <v>3271.212</v>
       </c>
       <c r="G85">
         <v>359.5</v>
@@ -8263,28 +8263,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M85">
-        <v>245.0059902</v>
+        <v>247.9578696000001</v>
       </c>
       <c r="N85">
-        <v>287.5940097999999</v>
+        <v>284.6421303999998</v>
       </c>
       <c r="O85">
-        <v>86.27820293999996</v>
+        <v>85.39263911999994</v>
       </c>
       <c r="P85">
-        <v>201.3158068599999</v>
+        <v>199.2494912799999</v>
       </c>
       <c r="Q85">
-        <v>426.1158068599999</v>
+        <v>424.0494912799999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2340656369144805</v>
+        <v>0.2450331756828008</v>
       </c>
       <c r="T85">
-        <v>4.347936187401396</v>
+        <v>4.601228075815261</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.17382440145743</v>
+        <v>2.147945539535317</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08377570810924811</v>
+        <v>0.08372045794303454</v>
       </c>
       <c r="C86">
-        <v>852.0408438505087</v>
+        <v>818.5816375990421</v>
       </c>
       <c r="D86">
-        <v>3763.752843850508</v>
+        <v>3769.236637599043</v>
       </c>
       <c r="E86">
-        <v>2843.812</v>
+        <v>2882.755</v>
       </c>
       <c r="F86">
-        <v>3271.212</v>
+        <v>3310.155</v>
       </c>
       <c r="G86">
         <v>359.5</v>
@@ -8345,28 +8345,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M86">
-        <v>247.9578696</v>
+        <v>250.909749</v>
       </c>
       <c r="N86">
-        <v>284.6421303999999</v>
+        <v>281.6902509999999</v>
       </c>
       <c r="O86">
-        <v>85.39263911999997</v>
+        <v>84.50707529999995</v>
       </c>
       <c r="P86">
-        <v>199.24949128</v>
+        <v>197.1831756999999</v>
       </c>
       <c r="Q86">
-        <v>424.04949128</v>
+        <v>421.9831756999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2450331756828007</v>
+        <v>0.2574630529535636</v>
       </c>
       <c r="T86">
-        <v>4.601228075815257</v>
+        <v>4.888292216017635</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.147945539535318</v>
+        <v>2.122675592011372</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08372045794303454</v>
+        <v>0.08366520777682099</v>
       </c>
       <c r="C87">
-        <v>818.5816375990421</v>
+        <v>785.1384344561739</v>
       </c>
       <c r="D87">
-        <v>3769.236637599043</v>
+        <v>3774.736434456173</v>
       </c>
       <c r="E87">
-        <v>2882.755</v>
+        <v>2921.698</v>
       </c>
       <c r="F87">
-        <v>3310.155</v>
+        <v>3349.098</v>
       </c>
       <c r="G87">
         <v>359.5</v>
@@ -8427,28 +8427,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M87">
-        <v>250.909749</v>
+        <v>253.8616284</v>
       </c>
       <c r="N87">
-        <v>281.6902509999999</v>
+        <v>278.7383715999999</v>
       </c>
       <c r="O87">
-        <v>84.50707529999995</v>
+        <v>83.62151147999997</v>
       </c>
       <c r="P87">
-        <v>197.1831756999999</v>
+        <v>195.1168601199999</v>
       </c>
       <c r="Q87">
-        <v>421.9831756999999</v>
+        <v>419.9168601199999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2574630529535636</v>
+        <v>0.2716686269772927</v>
       </c>
       <c r="T87">
-        <v>4.888292216017635</v>
+        <v>5.216365519106066</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.122675592011372</v>
+        <v>2.097993317685659</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08366520777682099</v>
+        <v>0.08360995761060742</v>
       </c>
       <c r="C88">
-        <v>785.1384344561739</v>
+        <v>751.7113045759952</v>
       </c>
       <c r="D88">
-        <v>3774.736434456173</v>
+        <v>3780.252304575995</v>
       </c>
       <c r="E88">
-        <v>2921.698</v>
+        <v>2960.641</v>
       </c>
       <c r="F88">
-        <v>3349.098</v>
+        <v>3388.041</v>
       </c>
       <c r="G88">
         <v>359.5</v>
@@ -8509,28 +8509,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M88">
-        <v>253.8616284</v>
+        <v>256.8135078</v>
       </c>
       <c r="N88">
-        <v>278.7383715999999</v>
+        <v>275.7864921999999</v>
       </c>
       <c r="O88">
-        <v>83.62151147999997</v>
+        <v>82.73594765999997</v>
       </c>
       <c r="P88">
-        <v>195.1168601199999</v>
+        <v>193.0505445399999</v>
       </c>
       <c r="Q88">
-        <v>419.9168601199999</v>
+        <v>417.8505445399999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2716686269772927</v>
+        <v>0.2880596739277494</v>
       </c>
       <c r="T88">
-        <v>5.216365519106066</v>
+        <v>5.594911638054258</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.097993317685659</v>
+        <v>2.073878451965134</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08360995761060742</v>
+        <v>0.08355470744439386</v>
       </c>
       <c r="C89">
-        <v>751.7113045759952</v>
+        <v>718.3003185232528</v>
       </c>
       <c r="D89">
-        <v>3780.252304575995</v>
+        <v>3785.784318523253</v>
       </c>
       <c r="E89">
-        <v>2960.641</v>
+        <v>2999.584</v>
       </c>
       <c r="F89">
-        <v>3388.041</v>
+        <v>3426.984</v>
       </c>
       <c r="G89">
         <v>359.5</v>
@@ -8591,28 +8591,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M89">
-        <v>256.8135078</v>
+        <v>259.7653872000001</v>
       </c>
       <c r="N89">
-        <v>275.7864921999999</v>
+        <v>272.8346127999998</v>
       </c>
       <c r="O89">
-        <v>82.73594765999997</v>
+        <v>81.85038383999995</v>
       </c>
       <c r="P89">
-        <v>193.0505445399999</v>
+        <v>190.9842289599999</v>
       </c>
       <c r="Q89">
-        <v>417.8505445399999</v>
+        <v>415.7842289599999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2880596739277494</v>
+        <v>0.3071825620366155</v>
       </c>
       <c r="T89">
-        <v>5.594911638054258</v>
+        <v>6.036548776827148</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.073878451965134</v>
+        <v>2.050311651374621</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08355470744439386</v>
+        <v>0.08349945727818031</v>
       </c>
       <c r="C90">
-        <v>718.3003185232528</v>
+        <v>684.9055472763525</v>
       </c>
       <c r="D90">
-        <v>3785.784318523253</v>
+        <v>3791.332547276353</v>
       </c>
       <c r="E90">
-        <v>2999.584</v>
+        <v>3038.527</v>
       </c>
       <c r="F90">
-        <v>3426.984</v>
+        <v>3465.927</v>
       </c>
       <c r="G90">
         <v>359.5</v>
@@ -8673,28 +8673,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M90">
-        <v>259.7653872000001</v>
+        <v>262.7172666</v>
       </c>
       <c r="N90">
-        <v>272.8346127999998</v>
+        <v>269.8827333999999</v>
       </c>
       <c r="O90">
-        <v>81.85038383999995</v>
+        <v>80.96482001999996</v>
       </c>
       <c r="P90">
-        <v>190.9842289599999</v>
+        <v>188.9179133799999</v>
       </c>
       <c r="Q90">
-        <v>415.7842289599999</v>
+        <v>413.7179133799999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3071825620366155</v>
+        <v>0.3297823388925482</v>
       </c>
       <c r="T90">
-        <v>6.036548776827148</v>
+        <v>6.558483577195108</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.050311651374621</v>
+        <v>2.027274441808614</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08349945727818031</v>
+        <v>0.08344420711196673</v>
       </c>
       <c r="C91">
-        <v>684.9055472763525</v>
+        <v>651.5270622304038</v>
       </c>
       <c r="D91">
-        <v>3791.332547276353</v>
+        <v>3796.897062230405</v>
       </c>
       <c r="E91">
-        <v>3038.527</v>
+        <v>3077.47</v>
       </c>
       <c r="F91">
-        <v>3465.927</v>
+        <v>3504.87</v>
       </c>
       <c r="G91">
         <v>359.5</v>
@@ -8755,28 +8755,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M91">
-        <v>262.7172666</v>
+        <v>265.6691460000001</v>
       </c>
       <c r="N91">
-        <v>269.8827333999999</v>
+        <v>266.9308539999998</v>
       </c>
       <c r="O91">
-        <v>80.96482001999996</v>
+        <v>80.07925619999995</v>
       </c>
       <c r="P91">
-        <v>188.9179133799999</v>
+        <v>186.8515977999999</v>
       </c>
       <c r="Q91">
-        <v>413.7179133799999</v>
+        <v>411.6515977999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3297823388925482</v>
+        <v>0.3569020711196674</v>
       </c>
       <c r="T91">
-        <v>6.558483577195108</v>
+        <v>7.18480533763666</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.027274441808614</v>
+        <v>2.004749170232962</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08344420711196673</v>
+        <v>0.09243435694575317</v>
       </c>
       <c r="C92">
-        <v>651.5270622304038</v>
+        <v>-119.3800030749576</v>
       </c>
       <c r="D92">
-        <v>3796.897062230405</v>
+        <v>3064.932996925043</v>
       </c>
       <c r="E92">
-        <v>3077.47</v>
+        <v>3116.413</v>
       </c>
       <c r="F92">
-        <v>3504.87</v>
+        <v>3543.813</v>
       </c>
       <c r="G92">
         <v>359.5</v>
@@ -8837,45 +8837,45 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M92">
-        <v>265.6691460000001</v>
+        <v>318.94317</v>
       </c>
       <c r="N92">
-        <v>266.9308539999998</v>
+        <v>213.6568299999999</v>
       </c>
       <c r="O92">
-        <v>80.07925619999995</v>
+        <v>64.09704899999997</v>
       </c>
       <c r="P92">
-        <v>186.8515977999999</v>
+        <v>149.5597809999999</v>
       </c>
       <c r="Q92">
-        <v>411.6515977999999</v>
+        <v>374.3597809999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3569020711196674</v>
+        <v>0.3900484105083687</v>
       </c>
       <c r="T92">
-        <v>7.18480533763666</v>
+        <v>7.950309711509669</v>
       </c>
       <c r="U92">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V92">
         <v>0.3</v>
       </c>
       <c r="W92">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.004749170232962</v>
+        <v>1.669889968172072</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09243435694575317</v>
+        <v>0.09247850677953962</v>
       </c>
       <c r="C93">
-        <v>-119.3800030749576</v>
+        <v>-161.2219021982728</v>
       </c>
       <c r="D93">
-        <v>3064.932996925043</v>
+        <v>3062.034097801728</v>
       </c>
       <c r="E93">
-        <v>3116.413</v>
+        <v>3155.356</v>
       </c>
       <c r="F93">
-        <v>3543.813</v>
+        <v>3582.756</v>
       </c>
       <c r="G93">
         <v>359.5</v>
@@ -8919,28 +8919,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M93">
-        <v>318.94317</v>
+        <v>322.44804</v>
       </c>
       <c r="N93">
-        <v>213.6568299999999</v>
+        <v>210.1519599999999</v>
       </c>
       <c r="O93">
-        <v>64.09704899999997</v>
+        <v>63.04558799999997</v>
       </c>
       <c r="P93">
-        <v>149.5597809999999</v>
+        <v>147.1063719999999</v>
       </c>
       <c r="Q93">
-        <v>374.3597809999999</v>
+        <v>371.9063719999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3900484105083687</v>
+        <v>0.4314813347442453</v>
       </c>
       <c r="T93">
-        <v>7.950309711509669</v>
+        <v>8.90719017885093</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.669889968172072</v>
+        <v>1.651738990257159</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09247850677953962</v>
+        <v>0.09252265661332605</v>
       </c>
       <c r="C94">
-        <v>-161.2219021982728</v>
+        <v>-203.058322784032</v>
       </c>
       <c r="D94">
-        <v>3062.034097801728</v>
+        <v>3059.140677215968</v>
       </c>
       <c r="E94">
-        <v>3155.356</v>
+        <v>3194.299</v>
       </c>
       <c r="F94">
-        <v>3582.756</v>
+        <v>3621.699000000001</v>
       </c>
       <c r="G94">
         <v>359.5</v>
@@ -9001,28 +9001,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M94">
-        <v>322.44804</v>
+        <v>325.95291</v>
       </c>
       <c r="N94">
-        <v>210.1519599999999</v>
+        <v>206.6470899999999</v>
       </c>
       <c r="O94">
-        <v>63.04558799999997</v>
+        <v>61.99412699999996</v>
       </c>
       <c r="P94">
-        <v>147.1063719999999</v>
+        <v>144.6529629999999</v>
       </c>
       <c r="Q94">
-        <v>371.9063719999999</v>
+        <v>369.452963</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4314813347442453</v>
+        <v>0.4847522373332296</v>
       </c>
       <c r="T94">
-        <v>8.90719017885093</v>
+        <v>10.13746506543255</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.651738990257159</v>
+        <v>1.633978355953318</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09252265661332605</v>
+        <v>0.09256680644711249</v>
       </c>
       <c r="C95">
-        <v>-203.058322784032</v>
+        <v>-244.8892803481458</v>
       </c>
       <c r="D95">
-        <v>3059.140677215968</v>
+        <v>3056.252719651854</v>
       </c>
       <c r="E95">
-        <v>3194.299</v>
+        <v>3233.242</v>
       </c>
       <c r="F95">
-        <v>3621.699000000001</v>
+        <v>3660.642</v>
       </c>
       <c r="G95">
         <v>359.5</v>
@@ -9083,28 +9083,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M95">
-        <v>325.95291</v>
+        <v>329.45778</v>
       </c>
       <c r="N95">
-        <v>206.6470899999999</v>
+        <v>203.1422199999999</v>
       </c>
       <c r="O95">
-        <v>61.99412699999996</v>
+        <v>60.94266599999997</v>
       </c>
       <c r="P95">
-        <v>144.6529629999999</v>
+        <v>142.1995539999999</v>
       </c>
       <c r="Q95">
-        <v>369.452963</v>
+        <v>366.9995539999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4847522373332296</v>
+        <v>0.5557801074518752</v>
       </c>
       <c r="T95">
-        <v>10.13746506543255</v>
+        <v>11.77783158087472</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.633978355953318</v>
+        <v>1.61659560748573</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09256680644711249</v>
+        <v>0.09261095628089894</v>
       </c>
       <c r="C96">
-        <v>-244.8892803481458</v>
+        <v>-286.7147903479918</v>
       </c>
       <c r="D96">
-        <v>3056.252719651854</v>
+        <v>3053.370209652009</v>
       </c>
       <c r="E96">
-        <v>3233.242</v>
+        <v>3272.185</v>
       </c>
       <c r="F96">
-        <v>3660.642</v>
+        <v>3699.585</v>
       </c>
       <c r="G96">
         <v>359.5</v>
@@ -9165,28 +9165,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M96">
-        <v>329.45778</v>
+        <v>332.9626500000001</v>
       </c>
       <c r="N96">
-        <v>203.1422199999999</v>
+        <v>199.6373499999999</v>
       </c>
       <c r="O96">
-        <v>60.94266599999997</v>
+        <v>59.89120499999996</v>
       </c>
       <c r="P96">
-        <v>142.1995539999999</v>
+        <v>139.7461449999999</v>
       </c>
       <c r="Q96">
-        <v>366.9995539999999</v>
+        <v>364.5461449999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5557801074518752</v>
+        <v>0.6552191256179793</v>
       </c>
       <c r="T96">
-        <v>11.77783158087472</v>
+        <v>14.07434470249375</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.61659560748573</v>
+        <v>1.599578811617459</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09261095628089894</v>
+        <v>0.09265510611468536</v>
       </c>
       <c r="C97">
-        <v>-286.7147903479918</v>
+        <v>-328.5348681826804</v>
       </c>
       <c r="D97">
-        <v>3053.370209652009</v>
+        <v>3050.49313181732</v>
       </c>
       <c r="E97">
-        <v>3272.185</v>
+        <v>3311.128</v>
       </c>
       <c r="F97">
-        <v>3699.585</v>
+        <v>3738.528</v>
       </c>
       <c r="G97">
         <v>359.5</v>
@@ -9247,28 +9247,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M97">
-        <v>332.9626500000001</v>
+        <v>336.46752</v>
       </c>
       <c r="N97">
-        <v>199.6373499999999</v>
+        <v>196.1324799999999</v>
       </c>
       <c r="O97">
-        <v>59.89120499999996</v>
+        <v>58.83974399999996</v>
       </c>
       <c r="P97">
-        <v>139.7461449999999</v>
+        <v>137.2927359999999</v>
       </c>
       <c r="Q97">
-        <v>364.5461449999999</v>
+        <v>362.0927359999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6552191256179793</v>
+        <v>0.8043776528671355</v>
       </c>
       <c r="T97">
-        <v>14.07434470249375</v>
+        <v>17.5191143849223</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.599578811617459</v>
+        <v>1.582916532329777</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09265510611468536</v>
+        <v>0.09269925594847181</v>
       </c>
       <c r="C98">
-        <v>-328.5348681826804</v>
+        <v>-370.3495291933455</v>
       </c>
       <c r="D98">
-        <v>3050.49313181732</v>
+        <v>3047.621470806655</v>
       </c>
       <c r="E98">
-        <v>3311.128</v>
+        <v>3350.071</v>
       </c>
       <c r="F98">
-        <v>3738.528</v>
+        <v>3777.471</v>
       </c>
       <c r="G98">
         <v>359.5</v>
@@ -9329,28 +9329,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M98">
-        <v>336.46752</v>
+        <v>339.97239</v>
       </c>
       <c r="N98">
-        <v>196.1324799999999</v>
+        <v>192.6276099999999</v>
       </c>
       <c r="O98">
-        <v>58.83974399999996</v>
+        <v>57.78828299999998</v>
       </c>
       <c r="P98">
-        <v>137.2927359999999</v>
+        <v>134.839327</v>
       </c>
       <c r="Q98">
-        <v>362.0927359999999</v>
+        <v>359.639327</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8043776528671334</v>
+        <v>1.052975198282393</v>
       </c>
       <c r="T98">
-        <v>17.51911438492225</v>
+        <v>23.2603971889698</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.582916532329777</v>
+        <v>1.566597805192357</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09269925594847181</v>
+        <v>0.09274340578225825</v>
       </c>
       <c r="C99">
-        <v>-370.3495291933455</v>
+        <v>-412.158788663402</v>
       </c>
       <c r="D99">
-        <v>3047.621470806655</v>
+        <v>3044.755211336598</v>
       </c>
       <c r="E99">
-        <v>3350.071</v>
+        <v>3389.014</v>
       </c>
       <c r="F99">
-        <v>3777.471</v>
+        <v>3816.414</v>
       </c>
       <c r="G99">
         <v>359.5</v>
@@ -9411,28 +9411,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M99">
-        <v>339.97239</v>
+        <v>343.47726</v>
       </c>
       <c r="N99">
-        <v>192.6276099999999</v>
+        <v>189.1227399999999</v>
       </c>
       <c r="O99">
-        <v>57.78828299999998</v>
+        <v>56.73682199999997</v>
       </c>
       <c r="P99">
-        <v>134.839327</v>
+        <v>132.3859179999999</v>
       </c>
       <c r="Q99">
-        <v>359.639327</v>
+        <v>357.185918</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.052975198282393</v>
+        <v>1.550170289112911</v>
       </c>
       <c r="T99">
-        <v>23.2603971889698</v>
+        <v>34.74296279706491</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.566597805192357</v>
+        <v>1.550612113302639</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09274340578225825</v>
+        <v>0.09278755561604468</v>
       </c>
       <c r="C100">
-        <v>-412.158788663402</v>
+        <v>-453.9626618188245</v>
       </c>
       <c r="D100">
-        <v>3044.755211336598</v>
+        <v>3041.894338181175</v>
       </c>
       <c r="E100">
-        <v>3389.014</v>
+        <v>3427.957</v>
       </c>
       <c r="F100">
-        <v>3816.414</v>
+        <v>3855.357</v>
       </c>
       <c r="G100">
         <v>359.5</v>
@@ -9493,28 +9493,28 @@
         <v>532.5999999999999</v>
       </c>
       <c r="M100">
-        <v>343.47726</v>
+        <v>346.98213</v>
       </c>
       <c r="N100">
-        <v>189.1227399999999</v>
+        <v>185.6178699999999</v>
       </c>
       <c r="O100">
-        <v>56.73682199999997</v>
+        <v>55.68536099999998</v>
       </c>
       <c r="P100">
-        <v>132.3859179999999</v>
+        <v>129.932509</v>
       </c>
       <c r="Q100">
-        <v>357.185918</v>
+        <v>354.7325089999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.550170289112911</v>
+        <v>3.041755561604465</v>
       </c>
       <c r="T100">
-        <v>34.74296279706491</v>
+        <v>69.19065962135024</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.550612113302639</v>
+        <v>1.53494936468342</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09278755561604468</v>
-      </c>
-      <c r="C101">
-        <v>-453.9626618188245</v>
-      </c>
-      <c r="D101">
-        <v>3041.894338181175</v>
-      </c>
-      <c r="E101">
-        <v>3427.957</v>
-      </c>
-      <c r="F101">
-        <v>3855.357</v>
-      </c>
-      <c r="G101">
-        <v>359.5</v>
-      </c>
-      <c r="H101">
-        <v>3466.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>757.4</v>
-      </c>
-      <c r="K101">
-        <v>224.8</v>
-      </c>
-      <c r="L101">
-        <v>532.5999999999999</v>
-      </c>
-      <c r="M101">
-        <v>346.98213</v>
-      </c>
-      <c r="N101">
-        <v>185.6178699999999</v>
-      </c>
-      <c r="O101">
-        <v>55.68536099999998</v>
-      </c>
-      <c r="P101">
-        <v>129.932509</v>
-      </c>
-      <c r="Q101">
-        <v>354.7325089999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.041755561604465</v>
-      </c>
-      <c r="T101">
-        <v>69.19065962135024</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.53494936468342</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
